--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -1,42 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\2025-0\Mota\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F18B85CB-2115-41A1-A6C2-E611265CB074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8570D3-1BBB-4109-95E8-4C57BB43C449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" xr2:uid="{878F31C5-4CEA-4304-87C5-39FC92D222CB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{878F31C5-4CEA-4304-87C5-39FC92D222CB}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BS!$A$1:$B$166</definedName>
+  </definedNames>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="314">
   <si>
     <t>DNI</t>
   </si>
@@ -92,9 +87,6 @@
     <t>40303753</t>
   </si>
   <si>
-    <t>24381542</t>
-  </si>
-  <si>
     <t>47906470</t>
   </si>
   <si>
@@ -182,9 +174,6 @@
     <t>72019595</t>
   </si>
   <si>
-    <t>42197272</t>
-  </si>
-  <si>
     <t>41968733</t>
   </si>
   <si>
@@ -197,9 +186,6 @@
     <t>02542365</t>
   </si>
   <si>
-    <t>00522190</t>
-  </si>
-  <si>
     <t>43958280</t>
   </si>
   <si>
@@ -326,9 +312,6 @@
     <t>31662709</t>
   </si>
   <si>
-    <t>77031404</t>
-  </si>
-  <si>
     <t>43769088</t>
   </si>
   <si>
@@ -431,9 +414,6 @@
     <t>80113798</t>
   </si>
   <si>
-    <t>44959881</t>
-  </si>
-  <si>
     <t>74497311</t>
   </si>
   <si>
@@ -518,9 +498,6 @@
     <t>BALBIN RAMOS CESAR ALBERTO</t>
   </si>
   <si>
-    <t>BANDA ORCCOSUPA ROSENDO</t>
-  </si>
-  <si>
     <t>BAUTISTA GUILLEN WILFREDO</t>
   </si>
   <si>
@@ -611,9 +588,6 @@
     <t>ESCALANTE GUERRA JUAN CARLOS</t>
   </si>
   <si>
-    <t>ESTEBA CRUZ MARCELO</t>
-  </si>
-  <si>
     <t>FERNANDEZ ALANYA JERONIMO ALBERTO</t>
   </si>
   <si>
@@ -626,9 +600,6 @@
     <t>GEMIO LAYME ANGELINO</t>
   </si>
   <si>
-    <t>GOMEZ SIXTO JUAN CARLOS</t>
-  </si>
-  <si>
     <t>GOMEZ VICHATA JORGE</t>
   </si>
   <si>
@@ -773,9 +744,6 @@
     <t>MORALES FELIX GABRIEL ANTONIO</t>
   </si>
   <si>
-    <t>MULLISACA ACARAPI LEO RODRIGO</t>
-  </si>
-  <si>
     <t>ÑAHUI QUISPE FREDDY AMERICO</t>
   </si>
   <si>
@@ -854,9 +822,6 @@
     <t>RAMOS VILLALBA DEMETRIO CALIXTO</t>
   </si>
   <si>
-    <t>RENGIFO SEGOVIA GRECIA MARGHIORI</t>
-  </si>
-  <si>
     <t>REYES LOARTE BRITHZA NATHALY</t>
   </si>
   <si>
@@ -905,9 +870,6 @@
     <t>TITO LAURA SAUL ISMAEL</t>
   </si>
   <si>
-    <t>TORRICO JUAREZ MARCIAL</t>
-  </si>
-  <si>
     <t>TRUJILLO CRESPO CRIS YORDI</t>
   </si>
   <si>
@@ -942,6 +904,75 @@
   </si>
   <si>
     <t>ZUÑIGA CAMA MANUEL EDUARDO</t>
+  </si>
+  <si>
+    <t>40362968</t>
+  </si>
+  <si>
+    <t>24687727</t>
+  </si>
+  <si>
+    <t>44025677</t>
+  </si>
+  <si>
+    <t>42252434</t>
+  </si>
+  <si>
+    <t>42431271</t>
+  </si>
+  <si>
+    <t>40434746</t>
+  </si>
+  <si>
+    <t>76834183</t>
+  </si>
+  <si>
+    <t>71932329</t>
+  </si>
+  <si>
+    <t>02550498</t>
+  </si>
+  <si>
+    <t>70355875</t>
+  </si>
+  <si>
+    <t>AREVALO DE LA ROCA JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>BUENDIA SOTO SEYMER MAYCOL</t>
+  </si>
+  <si>
+    <t>CHAVEZ QUISPE JORGE</t>
+  </si>
+  <si>
+    <t>CHUNGA QUINCHO ALFREDO</t>
+  </si>
+  <si>
+    <t>CORDOVA NORABUENA HITLER</t>
+  </si>
+  <si>
+    <t>GIL ENCISO DEIVIS RAFAEL</t>
+  </si>
+  <si>
+    <t>HUANACUNI CHOQUE GENARO WALTER</t>
+  </si>
+  <si>
+    <t>HUAQUISTO AMPUERO LELICIO</t>
+  </si>
+  <si>
+    <t>MAMANI PACORICONA OMAR BRAYAN</t>
+  </si>
+  <si>
+    <t>MESTAS ROMERO JUAN DANIEL</t>
+  </si>
+  <si>
+    <t>OCHOCHOQUE LUNA FIDEL</t>
+  </si>
+  <si>
+    <t>ROJAS QUISPE RUBEN EDY</t>
+  </si>
+  <si>
+    <t>VILLARROEL LOPEZ LUIS KAROL</t>
   </si>
 </sst>
 </file>
@@ -1319,10 +1350,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD330490-A8A1-49E3-86FF-A6622C7A89BB}">
-  <dimension ref="A1:B159"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <dimension ref="A1:B166"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="45.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1338,7 +1369,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1346,7 +1377,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1354,7 +1385,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1362,7 +1393,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1370,7 +1401,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1378,7 +1409,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1386,7 +1417,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1394,7 +1425,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1402,7 +1433,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1410,1197 +1441,1251 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="1" t="s">
-        <v>12</v>
+      <c r="A12" s="1">
+        <v>40752658</v>
       </c>
       <c r="B12" t="s">
-        <v>154</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="1" t="s">
-        <v>22</v>
+      <c r="A22" s="1">
+        <v>70295470</v>
       </c>
       <c r="B22" t="s">
-        <v>164</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="2">
+      <c r="A30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="1">
         <v>71831646</v>
       </c>
-      <c r="B30" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="B31" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>33</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s">
-        <v>176</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>38</v>
+        <v>292</v>
       </c>
       <c r="B39" t="s">
-        <v>181</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B42" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>42</v>
+        <v>293</v>
       </c>
       <c r="B43" t="s">
-        <v>185</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B45" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B47" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B48" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B49" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B50" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B53" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B54" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B56" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>56</v>
+        <v>294</v>
       </c>
       <c r="B57" t="s">
-        <v>199</v>
+        <v>306</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B58" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B59" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B60" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B61" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B62" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="2">
-        <v>31677451</v>
+      <c r="A63" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="B63" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B64" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B65" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="1" t="s">
-        <v>64</v>
+      <c r="A66" s="1">
+        <v>31677451</v>
       </c>
       <c r="B66" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B67" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B68" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B69" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>68</v>
+        <v>295</v>
       </c>
       <c r="B70" t="s">
-        <v>212</v>
+        <v>307</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="2">
-        <v>42305005</v>
+      <c r="A71" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="B71" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>69</v>
+        <v>296</v>
       </c>
       <c r="B72" t="s">
-        <v>214</v>
+        <v>308</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B73" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B74" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B75" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46881401</v>
+        <v>42305005</v>
       </c>
       <c r="B76" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B77" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B78" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="1">
-        <v>41996873</v>
+      <c r="A79" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B79" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B80" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="1" t="s">
-        <v>76</v>
+      <c r="A81" s="1">
+        <v>46881401</v>
       </c>
       <c r="B81" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B82" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B83" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="1" t="s">
-        <v>79</v>
+      <c r="A84" s="1">
+        <v>41996873</v>
       </c>
       <c r="B84" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B85" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B86" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="2">
-        <v>20427241</v>
+      <c r="A87" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="B87" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B88" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="2">
-        <v>46217452</v>
+      <c r="A89" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="B89" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B90" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B91" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="1" t="s">
-        <v>85</v>
+      <c r="A92" s="1">
+        <v>20427241</v>
       </c>
       <c r="B92" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B93" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="1" t="s">
-        <v>87</v>
+      <c r="A94" s="1">
+        <v>46217452</v>
       </c>
       <c r="B94" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B95" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B96" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B97" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B98" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B99" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="1" t="s">
-        <v>93</v>
+        <v>297</v>
       </c>
       <c r="B100" t="s">
-        <v>242</v>
+        <v>309</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B101" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="1" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B102" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B103" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B104" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B105" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="1" t="s">
-        <v>99</v>
+        <v>298</v>
       </c>
       <c r="B106" t="s">
-        <v>248</v>
+        <v>310</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B107" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="2">
-        <v>60820639</v>
+      <c r="A108" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="B108" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B109" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="1" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B110" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="1" t="s">
-        <v>103</v>
+        <v>299</v>
       </c>
       <c r="B111" t="s">
-        <v>253</v>
+        <v>311</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B112" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B113" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B114" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="1" t="s">
-        <v>107</v>
+      <c r="A115" s="1">
+        <v>60820639</v>
       </c>
       <c r="B115" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="1" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B116" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="1" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B117" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="1" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B118" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="1" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B119" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="1" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B120" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="1" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B121" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="2">
-        <v>43539336</v>
+      <c r="A122" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="B122" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="1" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B123" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B124" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="1" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B125" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="1">
-        <v>31601357</v>
+      <c r="A126" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="B126" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B127" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B128" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="1" t="s">
-        <v>119</v>
+      <c r="A129" s="1">
+        <v>43539336</v>
       </c>
       <c r="B129" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="2">
-        <v>61017018</v>
+      <c r="A130" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="B130" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="1" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B131" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="1" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="B132" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>40052591</v>
+        <v>31601357</v>
       </c>
       <c r="B133" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="1" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B134" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B135" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="1" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="B136" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="2">
-        <v>40782264</v>
+      <c r="A137" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="B137" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="2">
-        <v>76465704</v>
+      <c r="A138" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="B138" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="1" t="s">
-        <v>125</v>
+      <c r="A139" s="1">
+        <v>40052591</v>
       </c>
       <c r="B139" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B140" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="1" t="s">
-        <v>127</v>
+        <v>300</v>
       </c>
       <c r="B141" t="s">
-        <v>283</v>
+        <v>312</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="2">
-        <v>10663914</v>
+      <c r="A142" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="B142" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B143" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="1" t="s">
-        <v>129</v>
+      <c r="A144" s="1">
+        <v>40782264</v>
       </c>
       <c r="B144" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="1" t="s">
-        <v>130</v>
+      <c r="A145" s="1">
+        <v>76465704</v>
       </c>
       <c r="B145" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="2">
-        <v>42198740</v>
+      <c r="A146" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="B146" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="1" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B147" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="1" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="B148" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="1" t="s">
-        <v>133</v>
+      <c r="A149" s="1">
+        <v>10663914</v>
       </c>
       <c r="B149" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B150" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B151" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B152" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="1" t="s">
-        <v>137</v>
+      <c r="A153" s="1">
+        <v>42198740</v>
       </c>
       <c r="B153" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="1" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B154" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="1" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="B155" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B156" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="1" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="B157" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="1" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B158" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="1" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="B159" t="s">
-        <v>301</v>
+        <v>284</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>133</v>
+      </c>
+      <c r="B160" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>134</v>
+      </c>
+      <c r="B161" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162">
+        <v>43928099</v>
+      </c>
+      <c r="B162" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>135</v>
+      </c>
+      <c r="B163" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>136</v>
+      </c>
+      <c r="B164" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>137</v>
+      </c>
+      <c r="B165" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
+        <v>138</v>
+      </c>
+      <c r="B166" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B166" xr:uid="{AD330490-A8A1-49E3-86FF-A6622C7A89BB}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A2:A159" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8570D3-1BBB-4109-95E8-4C57BB43C449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7E5F14-6EA4-4907-A113-D1714011DFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{878F31C5-4CEA-4304-87C5-39FC92D222CB}"/>
   </bookViews>
@@ -1008,12 +1008,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1357,15 +1358,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
@@ -1373,7 +1374,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
@@ -1381,7 +1382,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
@@ -1389,7 +1390,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
@@ -1397,7 +1398,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
@@ -1405,7 +1406,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B7" t="s">
@@ -1413,7 +1414,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
@@ -1421,7 +1422,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
@@ -1429,7 +1430,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
@@ -1437,7 +1438,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
@@ -1445,7 +1446,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="1">
+      <c r="A12" s="3">
         <v>40752658</v>
       </c>
       <c r="B12" t="s">
@@ -1453,7 +1454,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B13" t="s">
@@ -1461,7 +1462,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B14" t="s">
@@ -1469,7 +1470,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B15" t="s">
@@ -1477,7 +1478,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B16" t="s">
@@ -1485,7 +1486,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B17" t="s">
@@ -1493,7 +1494,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B18" t="s">
@@ -1501,7 +1502,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B19" t="s">
@@ -1509,7 +1510,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B20" t="s">
@@ -1517,7 +1518,7 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B21" t="s">
@@ -1525,7 +1526,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="1">
+      <c r="A22" s="3">
         <v>70295470</v>
       </c>
       <c r="B22" t="s">
@@ -1533,7 +1534,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B23" t="s">
@@ -1541,7 +1542,7 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B24" t="s">
@@ -1549,7 +1550,7 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B25" t="s">
@@ -1557,7 +1558,7 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B26" t="s">
@@ -1565,7 +1566,7 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B27" t="s">
@@ -1573,7 +1574,7 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B28" t="s">
@@ -1581,7 +1582,7 @@
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B29" t="s">
@@ -1589,7 +1590,7 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B30" t="s">
@@ -1597,7 +1598,7 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="1">
+      <c r="A31" s="3">
         <v>71831646</v>
       </c>
       <c r="B31" t="s">
@@ -1605,7 +1606,7 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B32" t="s">
@@ -1613,7 +1614,7 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B33" t="s">
@@ -1621,7 +1622,7 @@
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="3" t="s">
         <v>291</v>
       </c>
       <c r="B34" t="s">
@@ -1629,7 +1630,7 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B35" t="s">
@@ -1637,7 +1638,7 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B36" t="s">
@@ -1645,7 +1646,7 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B37" t="s">
@@ -1653,7 +1654,7 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B38" t="s">
@@ -1661,7 +1662,7 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="3" t="s">
         <v>292</v>
       </c>
       <c r="B39" t="s">
@@ -1669,7 +1670,7 @@
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B40" t="s">
@@ -1677,7 +1678,7 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B41" t="s">
@@ -1685,7 +1686,7 @@
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B42" t="s">
@@ -1693,7 +1694,7 @@
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="3" t="s">
         <v>293</v>
       </c>
       <c r="B43" t="s">
@@ -1701,7 +1702,7 @@
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B44" t="s">
@@ -1709,7 +1710,7 @@
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B45" t="s">
@@ -1717,7 +1718,7 @@
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B46" t="s">
@@ -1725,7 +1726,7 @@
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B47" t="s">
@@ -1733,7 +1734,7 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B48" t="s">
@@ -1741,7 +1742,7 @@
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B49" t="s">
@@ -1749,7 +1750,7 @@
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B50" t="s">
@@ -1757,7 +1758,7 @@
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B51" t="s">
@@ -1765,7 +1766,7 @@
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B52" t="s">
@@ -1773,7 +1774,7 @@
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B53" t="s">
@@ -1781,7 +1782,7 @@
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B54" t="s">
@@ -1789,7 +1790,7 @@
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B55" t="s">
@@ -1797,7 +1798,7 @@
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B56" t="s">
@@ -1805,7 +1806,7 @@
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="3" t="s">
         <v>294</v>
       </c>
       <c r="B57" t="s">
@@ -1813,7 +1814,7 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B58" t="s">
@@ -1821,7 +1822,7 @@
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B59" t="s">
@@ -1829,7 +1830,7 @@
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B60" t="s">
@@ -1837,7 +1838,7 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B61" t="s">
@@ -1845,7 +1846,7 @@
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B62" t="s">
@@ -1853,7 +1854,7 @@
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B63" t="s">
@@ -1861,7 +1862,7 @@
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="3" t="s">
         <v>57</v>
       </c>
       <c r="B64" t="s">
@@ -1869,7 +1870,7 @@
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="3" t="s">
         <v>58</v>
       </c>
       <c r="B65" t="s">
@@ -1877,7 +1878,7 @@
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="1">
+      <c r="A66" s="3">
         <v>31677451</v>
       </c>
       <c r="B66" t="s">
@@ -1885,7 +1886,7 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B67" t="s">
@@ -1893,7 +1894,7 @@
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B68" t="s">
@@ -1901,7 +1902,7 @@
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B69" t="s">
@@ -1909,7 +1910,7 @@
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="3" t="s">
         <v>295</v>
       </c>
       <c r="B70" t="s">
@@ -1917,7 +1918,7 @@
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="3" t="s">
         <v>62</v>
       </c>
       <c r="B71" t="s">
@@ -1925,7 +1926,7 @@
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="3" t="s">
         <v>296</v>
       </c>
       <c r="B72" t="s">
@@ -1933,7 +1934,7 @@
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B73" t="s">
@@ -1941,7 +1942,7 @@
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="3" t="s">
         <v>64</v>
       </c>
       <c r="B74" t="s">
@@ -1949,7 +1950,7 @@
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B75" t="s">
@@ -1957,7 +1958,7 @@
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="2">
+      <c r="A76" s="3">
         <v>42305005</v>
       </c>
       <c r="B76" t="s">
@@ -1965,7 +1966,7 @@
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B77" t="s">
@@ -1973,7 +1974,7 @@
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="3" t="s">
         <v>67</v>
       </c>
       <c r="B78" t="s">
@@ -1981,7 +1982,7 @@
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B79" t="s">
@@ -1989,7 +1990,7 @@
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="3" t="s">
         <v>69</v>
       </c>
       <c r="B80" t="s">
@@ -1997,7 +1998,7 @@
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="1">
+      <c r="A81" s="3">
         <v>46881401</v>
       </c>
       <c r="B81" t="s">
@@ -2005,7 +2006,7 @@
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B82" t="s">
@@ -2013,7 +2014,7 @@
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="3" t="s">
         <v>71</v>
       </c>
       <c r="B83" t="s">
@@ -2021,7 +2022,7 @@
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="1">
+      <c r="A84" s="3">
         <v>41996873</v>
       </c>
       <c r="B84" t="s">
@@ -2029,7 +2030,7 @@
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="3" t="s">
         <v>72</v>
       </c>
       <c r="B85" t="s">
@@ -2037,7 +2038,7 @@
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="3" t="s">
         <v>73</v>
       </c>
       <c r="B86" t="s">
@@ -2045,7 +2046,7 @@
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="2" t="s">
+      <c r="A87" s="3" t="s">
         <v>74</v>
       </c>
       <c r="B87" t="s">
@@ -2053,7 +2054,7 @@
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="1" t="s">
+      <c r="A88" s="3" t="s">
         <v>75</v>
       </c>
       <c r="B88" t="s">
@@ -2061,7 +2062,7 @@
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="2" t="s">
+      <c r="A89" s="3" t="s">
         <v>76</v>
       </c>
       <c r="B89" t="s">
@@ -2069,7 +2070,7 @@
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="1" t="s">
+      <c r="A90" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B90" t="s">
@@ -2077,7 +2078,7 @@
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="3" t="s">
         <v>78</v>
       </c>
       <c r="B91" t="s">
@@ -2085,7 +2086,7 @@
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="1">
+      <c r="A92" s="3">
         <v>20427241</v>
       </c>
       <c r="B92" t="s">
@@ -2093,7 +2094,7 @@
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="1" t="s">
+      <c r="A93" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B93" t="s">
@@ -2101,7 +2102,7 @@
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="1">
+      <c r="A94" s="3">
         <v>46217452</v>
       </c>
       <c r="B94" t="s">
@@ -2109,7 +2110,7 @@
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="1" t="s">
+      <c r="A95" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B95" t="s">
@@ -2117,7 +2118,7 @@
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="1" t="s">
+      <c r="A96" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B96" t="s">
@@ -2125,7 +2126,7 @@
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="1" t="s">
+      <c r="A97" s="3" t="s">
         <v>82</v>
       </c>
       <c r="B97" t="s">
@@ -2133,7 +2134,7 @@
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="1" t="s">
+      <c r="A98" s="3" t="s">
         <v>83</v>
       </c>
       <c r="B98" t="s">
@@ -2141,7 +2142,7 @@
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="1" t="s">
+      <c r="A99" s="3" t="s">
         <v>84</v>
       </c>
       <c r="B99" t="s">
@@ -2149,7 +2150,7 @@
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="1" t="s">
+      <c r="A100" s="3" t="s">
         <v>297</v>
       </c>
       <c r="B100" t="s">
@@ -2157,7 +2158,7 @@
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="1" t="s">
+      <c r="A101" s="3" t="s">
         <v>85</v>
       </c>
       <c r="B101" t="s">
@@ -2165,7 +2166,7 @@
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="1" t="s">
+      <c r="A102" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B102" t="s">
@@ -2173,7 +2174,7 @@
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="1" t="s">
+      <c r="A103" s="3" t="s">
         <v>87</v>
       </c>
       <c r="B103" t="s">
@@ -2181,7 +2182,7 @@
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="1" t="s">
+      <c r="A104" s="3" t="s">
         <v>88</v>
       </c>
       <c r="B104" t="s">
@@ -2189,7 +2190,7 @@
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="1" t="s">
+      <c r="A105" s="3" t="s">
         <v>89</v>
       </c>
       <c r="B105" t="s">
@@ -2197,7 +2198,7 @@
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="1" t="s">
+      <c r="A106" s="3" t="s">
         <v>298</v>
       </c>
       <c r="B106" t="s">
@@ -2205,7 +2206,7 @@
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="1" t="s">
+      <c r="A107" s="3" t="s">
         <v>90</v>
       </c>
       <c r="B107" t="s">
@@ -2213,7 +2214,7 @@
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="2" t="s">
+      <c r="A108" s="3" t="s">
         <v>91</v>
       </c>
       <c r="B108" t="s">
@@ -2221,7 +2222,7 @@
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="1" t="s">
+      <c r="A109" s="3" t="s">
         <v>92</v>
       </c>
       <c r="B109" t="s">
@@ -2229,7 +2230,7 @@
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="1" t="s">
+      <c r="A110" s="3" t="s">
         <v>93</v>
       </c>
       <c r="B110" t="s">
@@ -2237,7 +2238,7 @@
       </c>
     </row>
     <row r="111" spans="1:2">
-      <c r="A111" s="1" t="s">
+      <c r="A111" s="3" t="s">
         <v>299</v>
       </c>
       <c r="B111" t="s">
@@ -2245,7 +2246,7 @@
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="1" t="s">
+      <c r="A112" s="3" t="s">
         <v>94</v>
       </c>
       <c r="B112" t="s">
@@ -2253,7 +2254,7 @@
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="1" t="s">
+      <c r="A113" s="3" t="s">
         <v>95</v>
       </c>
       <c r="B113" t="s">
@@ -2261,7 +2262,7 @@
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="1" t="s">
+      <c r="A114" s="3" t="s">
         <v>96</v>
       </c>
       <c r="B114" t="s">
@@ -2269,7 +2270,7 @@
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="1">
+      <c r="A115" s="3">
         <v>60820639</v>
       </c>
       <c r="B115" t="s">
@@ -2277,7 +2278,7 @@
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="1" t="s">
+      <c r="A116" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B116" t="s">
@@ -2285,7 +2286,7 @@
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="1" t="s">
+      <c r="A117" s="3" t="s">
         <v>98</v>
       </c>
       <c r="B117" t="s">
@@ -2293,7 +2294,7 @@
       </c>
     </row>
     <row r="118" spans="1:2">
-      <c r="A118" s="1" t="s">
+      <c r="A118" s="3" t="s">
         <v>99</v>
       </c>
       <c r="B118" t="s">
@@ -2301,7 +2302,7 @@
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="1" t="s">
+      <c r="A119" s="3" t="s">
         <v>100</v>
       </c>
       <c r="B119" t="s">
@@ -2309,7 +2310,7 @@
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="1" t="s">
+      <c r="A120" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B120" t="s">
@@ -2317,7 +2318,7 @@
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="1" t="s">
+      <c r="A121" s="3" t="s">
         <v>102</v>
       </c>
       <c r="B121" t="s">
@@ -2325,7 +2326,7 @@
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="2" t="s">
+      <c r="A122" s="3" t="s">
         <v>103</v>
       </c>
       <c r="B122" t="s">
@@ -2333,7 +2334,7 @@
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="1" t="s">
+      <c r="A123" s="3" t="s">
         <v>104</v>
       </c>
       <c r="B123" t="s">
@@ -2341,7 +2342,7 @@
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="1" t="s">
+      <c r="A124" s="3" t="s">
         <v>105</v>
       </c>
       <c r="B124" t="s">
@@ -2349,7 +2350,7 @@
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="1" t="s">
+      <c r="A125" s="3" t="s">
         <v>106</v>
       </c>
       <c r="B125" t="s">
@@ -2357,7 +2358,7 @@
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="1" t="s">
+      <c r="A126" s="3" t="s">
         <v>107</v>
       </c>
       <c r="B126" t="s">
@@ -2365,7 +2366,7 @@
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="1" t="s">
+      <c r="A127" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B127" t="s">
@@ -2373,7 +2374,7 @@
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="1" t="s">
+      <c r="A128" s="3" t="s">
         <v>109</v>
       </c>
       <c r="B128" t="s">
@@ -2381,7 +2382,7 @@
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="1">
+      <c r="A129" s="3">
         <v>43539336</v>
       </c>
       <c r="B129" t="s">
@@ -2389,7 +2390,7 @@
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="2" t="s">
+      <c r="A130" s="3" t="s">
         <v>110</v>
       </c>
       <c r="B130" t="s">
@@ -2397,7 +2398,7 @@
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="1" t="s">
+      <c r="A131" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B131" t="s">
@@ -2405,7 +2406,7 @@
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="1" t="s">
+      <c r="A132" s="3" t="s">
         <v>112</v>
       </c>
       <c r="B132" t="s">
@@ -2413,7 +2414,7 @@
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="2">
+      <c r="A133" s="3">
         <v>31601357</v>
       </c>
       <c r="B133" t="s">
@@ -2421,7 +2422,7 @@
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="1" t="s">
+      <c r="A134" s="3" t="s">
         <v>113</v>
       </c>
       <c r="B134" t="s">
@@ -2429,7 +2430,7 @@
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="1" t="s">
+      <c r="A135" s="3" t="s">
         <v>114</v>
       </c>
       <c r="B135" t="s">
@@ -2437,7 +2438,7 @@
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="1" t="s">
+      <c r="A136" s="3" t="s">
         <v>115</v>
       </c>
       <c r="B136" t="s">
@@ -2445,7 +2446,7 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="2" t="s">
+      <c r="A137" s="3" t="s">
         <v>116</v>
       </c>
       <c r="B137" t="s">
@@ -2453,7 +2454,7 @@
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="2" t="s">
+      <c r="A138" s="3" t="s">
         <v>117</v>
       </c>
       <c r="B138" t="s">
@@ -2461,7 +2462,7 @@
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="1">
+      <c r="A139" s="3">
         <v>40052591</v>
       </c>
       <c r="B139" t="s">
@@ -2469,7 +2470,7 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="1" t="s">
+      <c r="A140" s="3" t="s">
         <v>118</v>
       </c>
       <c r="B140" t="s">
@@ -2477,7 +2478,7 @@
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="1" t="s">
+      <c r="A141" s="3" t="s">
         <v>300</v>
       </c>
       <c r="B141" t="s">
@@ -2485,7 +2486,7 @@
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="2" t="s">
+      <c r="A142" s="3" t="s">
         <v>119</v>
       </c>
       <c r="B142" t="s">
@@ -2493,7 +2494,7 @@
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="1" t="s">
+      <c r="A143" s="3" t="s">
         <v>120</v>
       </c>
       <c r="B143" t="s">
@@ -2501,7 +2502,7 @@
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="1">
+      <c r="A144" s="3">
         <v>40782264</v>
       </c>
       <c r="B144" t="s">
@@ -2509,7 +2510,7 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="1">
+      <c r="A145" s="3">
         <v>76465704</v>
       </c>
       <c r="B145" t="s">
@@ -2517,7 +2518,7 @@
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="2" t="s">
+      <c r="A146" s="3" t="s">
         <v>121</v>
       </c>
       <c r="B146" t="s">
@@ -2525,7 +2526,7 @@
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="1" t="s">
+      <c r="A147" s="3" t="s">
         <v>122</v>
       </c>
       <c r="B147" t="s">
@@ -2533,7 +2534,7 @@
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="1" t="s">
+      <c r="A148" s="3" t="s">
         <v>123</v>
       </c>
       <c r="B148" t="s">
@@ -2541,7 +2542,7 @@
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="1">
+      <c r="A149" s="3">
         <v>10663914</v>
       </c>
       <c r="B149" t="s">
@@ -2549,7 +2550,7 @@
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="1" t="s">
+      <c r="A150" s="3" t="s">
         <v>124</v>
       </c>
       <c r="B150" t="s">
@@ -2557,7 +2558,7 @@
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="1" t="s">
+      <c r="A151" s="3" t="s">
         <v>125</v>
       </c>
       <c r="B151" t="s">
@@ -2565,7 +2566,7 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="1" t="s">
+      <c r="A152" s="3" t="s">
         <v>126</v>
       </c>
       <c r="B152" t="s">
@@ -2573,7 +2574,7 @@
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="1">
+      <c r="A153" s="3">
         <v>42198740</v>
       </c>
       <c r="B153" t="s">
@@ -2581,7 +2582,7 @@
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="1" t="s">
+      <c r="A154" s="3" t="s">
         <v>127</v>
       </c>
       <c r="B154" t="s">
@@ -2589,7 +2590,7 @@
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="1" t="s">
+      <c r="A155" s="3" t="s">
         <v>128</v>
       </c>
       <c r="B155" t="s">
@@ -2597,7 +2598,7 @@
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="1" t="s">
+      <c r="A156" s="3" t="s">
         <v>129</v>
       </c>
       <c r="B156" t="s">
@@ -2605,7 +2606,7 @@
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="1" t="s">
+      <c r="A157" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B157" t="s">
@@ -2613,7 +2614,7 @@
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="1" t="s">
+      <c r="A158" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B158" t="s">
@@ -2621,7 +2622,7 @@
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="1" t="s">
+      <c r="A159" s="3" t="s">
         <v>132</v>
       </c>
       <c r="B159" t="s">
@@ -2629,7 +2630,7 @@
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" t="s">
+      <c r="A160" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B160" t="s">
@@ -2637,7 +2638,7 @@
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" t="s">
+      <c r="A161" s="2" t="s">
         <v>134</v>
       </c>
       <c r="B161" t="s">
@@ -2645,7 +2646,7 @@
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162">
+      <c r="A162" s="2">
         <v>43928099</v>
       </c>
       <c r="B162" t="s">
@@ -2653,7 +2654,7 @@
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" t="s">
+      <c r="A163" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B163" t="s">
@@ -2661,7 +2662,7 @@
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" t="s">
+      <c r="A164" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B164" t="s">
@@ -2669,7 +2670,7 @@
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" t="s">
+      <c r="A165" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B165" t="s">
@@ -2677,7 +2678,7 @@
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" t="s">
+      <c r="A166" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B166" t="s">

--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7E5F14-6EA4-4907-A113-D1714011DFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775D6D8F-7632-45F4-9538-D70FA613E24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{878F31C5-4CEA-4304-87C5-39FC92D222CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" xr2:uid="{878F31C5-4CEA-4304-87C5-39FC92D222CB}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="1" r:id="rId1"/>
@@ -18,20 +18,28 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BS!$A$1:$B$166</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="332">
   <si>
     <t>DNI</t>
   </si>
@@ -39,12 +47,6 @@
     <t>NOMBRE</t>
   </si>
   <si>
-    <t>09874967</t>
-  </si>
-  <si>
-    <t>00409316</t>
-  </si>
-  <si>
     <t>10604841</t>
   </si>
   <si>
@@ -60,18 +62,12 @@
     <t>74574889</t>
   </si>
   <si>
-    <t>01991139</t>
-  </si>
-  <si>
     <t>73386474</t>
   </si>
   <si>
     <t>70367111</t>
   </si>
   <si>
-    <t>02546314</t>
-  </si>
-  <si>
     <t>32980742</t>
   </si>
   <si>
@@ -93,9 +89,6 @@
     <t>40896187</t>
   </si>
   <si>
-    <t>09963107</t>
-  </si>
-  <si>
     <t>41137298</t>
   </si>
   <si>
@@ -117,9 +110,6 @@
     <t>40409818</t>
   </si>
   <si>
-    <t>01539176</t>
-  </si>
-  <si>
     <t>75716072</t>
   </si>
   <si>
@@ -132,9 +122,6 @@
     <t>43952255</t>
   </si>
   <si>
-    <t>02044816</t>
-  </si>
-  <si>
     <t>20068854</t>
   </si>
   <si>
@@ -159,9 +146,6 @@
     <t>41648714</t>
   </si>
   <si>
-    <t>01298035</t>
-  </si>
-  <si>
     <t>40604738</t>
   </si>
   <si>
@@ -183,9 +167,6 @@
     <t>42966692</t>
   </si>
   <si>
-    <t>02542365</t>
-  </si>
-  <si>
     <t>43958280</t>
   </si>
   <si>
@@ -225,18 +206,12 @@
     <t>46513926</t>
   </si>
   <si>
-    <t>08769965</t>
-  </si>
-  <si>
     <t>44352393</t>
   </si>
   <si>
     <t>40947821</t>
   </si>
   <si>
-    <t>09244927</t>
-  </si>
-  <si>
     <t>47595131</t>
   </si>
   <si>
@@ -246,9 +221,6 @@
     <t>10727102</t>
   </si>
   <si>
-    <t>06808878</t>
-  </si>
-  <si>
     <t>48619119</t>
   </si>
   <si>
@@ -279,24 +251,15 @@
     <t>80569866</t>
   </si>
   <si>
-    <t>02553630</t>
-  </si>
-  <si>
     <t>41997576</t>
   </si>
   <si>
     <t>61195518</t>
   </si>
   <si>
-    <t>00676531</t>
-  </si>
-  <si>
     <t>40662325</t>
   </si>
   <si>
-    <t>02425316</t>
-  </si>
-  <si>
     <t>73304687</t>
   </si>
   <si>
@@ -336,12 +299,6 @@
     <t>43700994</t>
   </si>
   <si>
-    <t>01332505</t>
-  </si>
-  <si>
-    <t>04743900</t>
-  </si>
-  <si>
     <t>46912053</t>
   </si>
   <si>
@@ -378,9 +335,6 @@
     <t>47604404</t>
   </si>
   <si>
-    <t>02527553</t>
-  </si>
-  <si>
     <t>72709468</t>
   </si>
   <si>
@@ -402,9 +356,6 @@
     <t>48149851</t>
   </si>
   <si>
-    <t>02545100</t>
-  </si>
-  <si>
     <t>75021649</t>
   </si>
   <si>
@@ -417,9 +368,6 @@
     <t>74497311</t>
   </si>
   <si>
-    <t>05958276</t>
-  </si>
-  <si>
     <t>47037763</t>
   </si>
   <si>
@@ -432,9 +380,6 @@
     <t>47656024</t>
   </si>
   <si>
-    <t>00444615</t>
-  </si>
-  <si>
     <t>44164626</t>
   </si>
   <si>
@@ -930,9 +875,6 @@
     <t>71932329</t>
   </si>
   <si>
-    <t>02550498</t>
-  </si>
-  <si>
     <t>70355875</t>
   </si>
   <si>
@@ -973,6 +915,126 @@
   </si>
   <si>
     <t>VILLARROEL LOPEZ LUIS KAROL</t>
+  </si>
+  <si>
+    <t>9874967</t>
+  </si>
+  <si>
+    <t>409316</t>
+  </si>
+  <si>
+    <t>1991139</t>
+  </si>
+  <si>
+    <t>40752658</t>
+  </si>
+  <si>
+    <t>2546314</t>
+  </si>
+  <si>
+    <t>9963107</t>
+  </si>
+  <si>
+    <t>70295470</t>
+  </si>
+  <si>
+    <t>1539176</t>
+  </si>
+  <si>
+    <t>71831646</t>
+  </si>
+  <si>
+    <t>2044816</t>
+  </si>
+  <si>
+    <t>1298035</t>
+  </si>
+  <si>
+    <t>2542365</t>
+  </si>
+  <si>
+    <t>31677451</t>
+  </si>
+  <si>
+    <t>8769965</t>
+  </si>
+  <si>
+    <t>42305005</t>
+  </si>
+  <si>
+    <t>9244927</t>
+  </si>
+  <si>
+    <t>46881401</t>
+  </si>
+  <si>
+    <t>6808878</t>
+  </si>
+  <si>
+    <t>41996873</t>
+  </si>
+  <si>
+    <t>20427241</t>
+  </si>
+  <si>
+    <t>46217452</t>
+  </si>
+  <si>
+    <t>2553630</t>
+  </si>
+  <si>
+    <t>676531</t>
+  </si>
+  <si>
+    <t>2425316</t>
+  </si>
+  <si>
+    <t>2550498</t>
+  </si>
+  <si>
+    <t>60820639</t>
+  </si>
+  <si>
+    <t>1332505</t>
+  </si>
+  <si>
+    <t>4743900</t>
+  </si>
+  <si>
+    <t>43539336</t>
+  </si>
+  <si>
+    <t>31601357</t>
+  </si>
+  <si>
+    <t>2527553</t>
+  </si>
+  <si>
+    <t>40052591</t>
+  </si>
+  <si>
+    <t>40782264</t>
+  </si>
+  <si>
+    <t>76465704</t>
+  </si>
+  <si>
+    <t>2545100</t>
+  </si>
+  <si>
+    <t>10663914</t>
+  </si>
+  <si>
+    <t>42198740</t>
+  </si>
+  <si>
+    <t>5958276</t>
+  </si>
+  <si>
+    <t>444615</t>
+  </si>
+  <si>
+    <t>43928099</t>
   </si>
 </sst>
 </file>
@@ -1352,9 +1414,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD330490-A8A1-49E3-86FF-A6622C7A89BB}">
   <dimension ref="A1:B166"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="45.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1367,1322 +1429,1322 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>292</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>3</v>
+        <v>293</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>9</v>
+        <v>294</v>
       </c>
       <c r="B9" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="3">
-        <v>40752658</v>
+      <c r="A12" s="3" t="s">
+        <v>295</v>
       </c>
       <c r="B12" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>12</v>
+        <v>296</v>
       </c>
       <c r="B13" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>20</v>
+        <v>297</v>
       </c>
       <c r="B21" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="3">
-        <v>70295470</v>
+      <c r="A22" s="3" t="s">
+        <v>298</v>
       </c>
       <c r="B22" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B28" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="3" t="s">
-        <v>28</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="3">
-        <v>71831646</v>
+      <c r="A31" s="3" t="s">
+        <v>300</v>
       </c>
       <c r="B31" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B33" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s">
-        <v>303</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="3" t="s">
-        <v>33</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="3" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="B39" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B42" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="B43" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B44" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B45" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B46" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B47" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="3" t="s">
-        <v>42</v>
+        <v>302</v>
       </c>
       <c r="B48" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B49" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B50" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B51" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="3" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B52" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B53" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="3" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="3" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B55" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="3" t="s">
-        <v>50</v>
+        <v>303</v>
       </c>
       <c r="B56" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="3" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="B57" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B58" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B59" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B60" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="3" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B62" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B63" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B64" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B65" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="3">
-        <v>31677451</v>
+      <c r="A66" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="B66" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B67" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B68" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B69" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="3" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="B70" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B71" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="3" t="s">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="B72" t="s">
-        <v>308</v>
+        <v>286</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B73" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="3" t="s">
-        <v>64</v>
+        <v>305</v>
       </c>
       <c r="B74" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B75" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="3">
-        <v>42305005</v>
+      <c r="A76" s="3" t="s">
+        <v>306</v>
       </c>
       <c r="B76" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B77" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="3" t="s">
-        <v>67</v>
+        <v>307</v>
       </c>
       <c r="B78" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B79" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B80" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="3">
-        <v>46881401</v>
+      <c r="A81" s="3" t="s">
+        <v>308</v>
       </c>
       <c r="B81" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B82" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="3" t="s">
-        <v>71</v>
+        <v>309</v>
       </c>
       <c r="B83" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="3">
-        <v>41996873</v>
+      <c r="A84" s="3" t="s">
+        <v>310</v>
       </c>
       <c r="B84" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="3" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B85" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B86" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B87" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="B88" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B89" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="3" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B90" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B91" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="3">
-        <v>20427241</v>
+      <c r="A92" s="3" t="s">
+        <v>311</v>
       </c>
       <c r="B92" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B93" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="3">
-        <v>46217452</v>
+      <c r="A94" s="3" t="s">
+        <v>312</v>
       </c>
       <c r="B94" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="3" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B95" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="3" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B96" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="3" t="s">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="B97" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B98" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="B99" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="3" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="B100" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="3" t="s">
-        <v>85</v>
+        <v>314</v>
       </c>
       <c r="B101" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="3" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B102" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="3" t="s">
-        <v>87</v>
+        <v>315</v>
       </c>
       <c r="B103" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="3" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="B104" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="3" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="B105" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="3" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="B106" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="3" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="B107" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="3" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="B108" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="3" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="B109" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="3" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="B110" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="3" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="B111" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="B112" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="B113" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B114" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="3">
-        <v>60820639</v>
+      <c r="A115" s="3" t="s">
+        <v>317</v>
       </c>
       <c r="B115" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="3" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="B116" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B117" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="3" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B118" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="3" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B119" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="3" t="s">
-        <v>101</v>
+        <v>318</v>
       </c>
       <c r="B120" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="3" t="s">
-        <v>102</v>
+        <v>319</v>
       </c>
       <c r="B121" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="3" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="B122" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="3" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="B123" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="3" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="B124" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="3" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="B125" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="3" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B126" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="3" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="B127" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="3" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="B128" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="3">
-        <v>43539336</v>
+      <c r="A129" s="3" t="s">
+        <v>320</v>
       </c>
       <c r="B129" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="3" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="B130" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="3" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="B131" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="3" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="B132" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="3">
-        <v>31601357</v>
+      <c r="A133" s="3" t="s">
+        <v>321</v>
       </c>
       <c r="B133" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="3" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="B134" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="3" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="B135" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="3" t="s">
-        <v>115</v>
+        <v>322</v>
       </c>
       <c r="B136" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="3" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="B137" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="3" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="B138" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="3">
-        <v>40052591</v>
+      <c r="A139" s="3" t="s">
+        <v>323</v>
       </c>
       <c r="B139" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="3" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="B140" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="3" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="B141" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="3" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B142" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="3" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="B143" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="3">
-        <v>40782264</v>
+      <c r="A144" s="3" t="s">
+        <v>324</v>
       </c>
       <c r="B144" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="3">
-        <v>76465704</v>
+      <c r="A145" s="3" t="s">
+        <v>325</v>
       </c>
       <c r="B145" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="3" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="B146" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B147" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="3" t="s">
-        <v>123</v>
+        <v>326</v>
       </c>
       <c r="B148" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="3">
-        <v>10663914</v>
+      <c r="A149" s="3" t="s">
+        <v>327</v>
       </c>
       <c r="B149" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="3" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="3" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B151" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="3" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="B152" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="3">
-        <v>42198740</v>
+      <c r="A153" s="3" t="s">
+        <v>328</v>
       </c>
       <c r="B153" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="3" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="B154" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="3" t="s">
-        <v>128</v>
+        <v>329</v>
       </c>
       <c r="B155" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="3" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="B156" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="3" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="B157" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="3" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="B158" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="3" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="B159" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2" t="s">
-        <v>133</v>
+        <v>330</v>
       </c>
       <c r="B160" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="B161" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="2">
-        <v>43928099</v>
+      <c r="A162" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="B162" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="B163" t="s">
-        <v>287</v>
+        <v>266</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="B164" t="s">
-        <v>288</v>
+        <v>267</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="B165" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="B166" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775D6D8F-7632-45F4-9538-D70FA613E24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BBC731B-1F95-4E67-A7B0-B073D59CA609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" xr2:uid="{878F31C5-4CEA-4304-87C5-39FC92D222CB}"/>
   </bookViews>
@@ -1041,8 +1041,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -1070,7 +1078,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1079,6 +1087,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1413,13 +1422,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD330490-A8A1-49E3-86FF-A6622C7A89BB}">
-  <dimension ref="A1:B166"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="45.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1427,7 +1436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
         <v>292</v>
       </c>
@@ -1435,7 +1444,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
         <v>293</v>
       </c>
@@ -1443,7 +1452,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1451,7 +1460,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -1459,15 +1468,16 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:8">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -1475,7 +1485,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:8">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -1483,7 +1493,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:8">
       <c r="A9" s="3" t="s">
         <v>294</v>
       </c>
@@ -1491,7 +1501,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:8">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -1499,7 +1509,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:8">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
@@ -1507,7 +1517,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:8">
       <c r="A12" s="3" t="s">
         <v>295</v>
       </c>
@@ -1515,7 +1525,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:8">
       <c r="A13" s="3" t="s">
         <v>296</v>
       </c>
@@ -1523,7 +1533,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:8">
       <c r="A14" s="3" t="s">
         <v>9</v>
       </c>
@@ -1531,7 +1541,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:8">
       <c r="A15" s="3" t="s">
         <v>10</v>
       </c>
@@ -1539,7 +1549,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:8">
       <c r="A16" s="3" t="s">
         <v>11</v>
       </c>
@@ -2748,7 +2758,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B166" xr:uid="{AD330490-A8A1-49E3-86FF-A6622C7A89BB}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB7D372-CDD8-4540-ABF8-9C2B1905C5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7CA2527-D1CC-47CC-AB67-E8D069B96124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" xr2:uid="{878F31C5-4CEA-4304-87C5-39FC92D222CB}"/>
+    <workbookView xWindow="96" yWindow="0" windowWidth="14868" windowHeight="12240" xr2:uid="{878F31C5-4CEA-4304-87C5-39FC92D222CB}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="1" r:id="rId1"/>
@@ -18,28 +18,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BS!$A$1:$B$166</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="316">
   <si>
     <t>DNI</t>
   </si>
@@ -47,6 +39,417 @@
     <t>NOMBRE</t>
   </si>
   <si>
+    <t>09874967</t>
+  </si>
+  <si>
+    <t>00409316</t>
+  </si>
+  <si>
+    <t>10604841</t>
+  </si>
+  <si>
+    <t>10108517</t>
+  </si>
+  <si>
+    <t>10264107</t>
+  </si>
+  <si>
+    <t>48716409</t>
+  </si>
+  <si>
+    <t>74574889</t>
+  </si>
+  <si>
+    <t>01991139</t>
+  </si>
+  <si>
+    <t>73386474</t>
+  </si>
+  <si>
+    <t>70367111</t>
+  </si>
+  <si>
+    <t>02546314</t>
+  </si>
+  <si>
+    <t>32980742</t>
+  </si>
+  <si>
+    <t>43728469</t>
+  </si>
+  <si>
+    <t>24494456</t>
+  </si>
+  <si>
+    <t>41004089</t>
+  </si>
+  <si>
+    <t>40303753</t>
+  </si>
+  <si>
+    <t>47906470</t>
+  </si>
+  <si>
+    <t>40896187</t>
+  </si>
+  <si>
+    <t>09963107</t>
+  </si>
+  <si>
+    <t>41137298</t>
+  </si>
+  <si>
+    <t>29631887</t>
+  </si>
+  <si>
+    <t>40974286</t>
+  </si>
+  <si>
+    <t>20440891</t>
+  </si>
+  <si>
+    <t>42950740</t>
+  </si>
+  <si>
+    <t>23996183</t>
+  </si>
+  <si>
+    <t>40409818</t>
+  </si>
+  <si>
+    <t>01539176</t>
+  </si>
+  <si>
+    <t>75716072</t>
+  </si>
+  <si>
+    <t>29547818</t>
+  </si>
+  <si>
+    <t>28714683</t>
+  </si>
+  <si>
+    <t>43952255</t>
+  </si>
+  <si>
+    <t>02044816</t>
+  </si>
+  <si>
+    <t>20068854</t>
+  </si>
+  <si>
+    <t>42177491</t>
+  </si>
+  <si>
+    <t>43548231</t>
+  </si>
+  <si>
+    <t>23274872</t>
+  </si>
+  <si>
+    <t>75102983</t>
+  </si>
+  <si>
+    <t>80064592</t>
+  </si>
+  <si>
+    <t>47590083</t>
+  </si>
+  <si>
+    <t>41648714</t>
+  </si>
+  <si>
+    <t>01298035</t>
+  </si>
+  <si>
+    <t>40604738</t>
+  </si>
+  <si>
+    <t>40329505</t>
+  </si>
+  <si>
+    <t>44235236</t>
+  </si>
+  <si>
+    <t>72019595</t>
+  </si>
+  <si>
+    <t>41968733</t>
+  </si>
+  <si>
+    <t>80317947</t>
+  </si>
+  <si>
+    <t>42966692</t>
+  </si>
+  <si>
+    <t>02542365</t>
+  </si>
+  <si>
+    <t>43958280</t>
+  </si>
+  <si>
+    <t>44275274</t>
+  </si>
+  <si>
+    <t>45089074</t>
+  </si>
+  <si>
+    <t>28274549</t>
+  </si>
+  <si>
+    <t>41672593</t>
+  </si>
+  <si>
+    <t>42725445</t>
+  </si>
+  <si>
+    <t>24698674</t>
+  </si>
+  <si>
+    <t>73598701</t>
+  </si>
+  <si>
+    <t>80533325</t>
+  </si>
+  <si>
+    <t>47800527</t>
+  </si>
+  <si>
+    <t>47399870</t>
+  </si>
+  <si>
+    <t>45384441</t>
+  </si>
+  <si>
+    <t>46513926</t>
+  </si>
+  <si>
+    <t>08769965</t>
+  </si>
+  <si>
+    <t>44352393</t>
+  </si>
+  <si>
+    <t>40947821</t>
+  </si>
+  <si>
+    <t>09244927</t>
+  </si>
+  <si>
+    <t>47595131</t>
+  </si>
+  <si>
+    <t>71019123</t>
+  </si>
+  <si>
+    <t>10727102</t>
+  </si>
+  <si>
+    <t>06808878</t>
+  </si>
+  <si>
+    <t>48619119</t>
+  </si>
+  <si>
+    <t>70013083</t>
+  </si>
+  <si>
+    <t>40891715</t>
+  </si>
+  <si>
+    <t>70417820</t>
+  </si>
+  <si>
+    <t>43973895</t>
+  </si>
+  <si>
+    <t>73415532</t>
+  </si>
+  <si>
+    <t>74574874</t>
+  </si>
+  <si>
+    <t>43032559</t>
+  </si>
+  <si>
+    <t>44241105</t>
+  </si>
+  <si>
+    <t>80569866</t>
+  </si>
+  <si>
+    <t>02553630</t>
+  </si>
+  <si>
+    <t>41997576</t>
+  </si>
+  <si>
+    <t>61195518</t>
+  </si>
+  <si>
+    <t>00676531</t>
+  </si>
+  <si>
+    <t>40662325</t>
+  </si>
+  <si>
+    <t>02425316</t>
+  </si>
+  <si>
+    <t>73304687</t>
+  </si>
+  <si>
+    <t>10070171</t>
+  </si>
+  <si>
+    <t>46219653</t>
+  </si>
+  <si>
+    <t>30766789</t>
+  </si>
+  <si>
+    <t>31662709</t>
+  </si>
+  <si>
+    <t>43769088</t>
+  </si>
+  <si>
+    <t>40324519</t>
+  </si>
+  <si>
+    <t>46361156</t>
+  </si>
+  <si>
+    <t>80548721</t>
+  </si>
+  <si>
+    <t>71333124</t>
+  </si>
+  <si>
+    <t>42036243</t>
+  </si>
+  <si>
+    <t>71790593</t>
+  </si>
+  <si>
+    <t>43700994</t>
+  </si>
+  <si>
+    <t>01332505</t>
+  </si>
+  <si>
+    <t>04743900</t>
+  </si>
+  <si>
+    <t>46912053</t>
+  </si>
+  <si>
+    <t>70768801</t>
+  </si>
+  <si>
+    <t>75972848</t>
+  </si>
+  <si>
+    <t>47056207</t>
+  </si>
+  <si>
+    <t>28281963</t>
+  </si>
+  <si>
+    <t>46766546</t>
+  </si>
+  <si>
+    <t>42535729</t>
+  </si>
+  <si>
+    <t>42656588</t>
+  </si>
+  <si>
+    <t>29725729</t>
+  </si>
+  <si>
+    <t>40203991</t>
+  </si>
+  <si>
+    <t>40229371</t>
+  </si>
+  <si>
+    <t>47604404</t>
+  </si>
+  <si>
+    <t>02527553</t>
+  </si>
+  <si>
+    <t>72709468</t>
+  </si>
+  <si>
+    <t>41586331</t>
+  </si>
+  <si>
+    <t>72251136</t>
+  </si>
+  <si>
+    <t>73547288</t>
+  </si>
+  <si>
+    <t>44978131</t>
+  </si>
+  <si>
+    <t>46265351</t>
+  </si>
+  <si>
+    <t>48149851</t>
+  </si>
+  <si>
+    <t>02545100</t>
+  </si>
+  <si>
+    <t>75021649</t>
+  </si>
+  <si>
+    <t>42492796</t>
+  </si>
+  <si>
+    <t>80113798</t>
+  </si>
+  <si>
+    <t>74497311</t>
+  </si>
+  <si>
+    <t>05958276</t>
+  </si>
+  <si>
+    <t>47037763</t>
+  </si>
+  <si>
+    <t>42972864</t>
+  </si>
+  <si>
+    <t>41445238</t>
+  </si>
+  <si>
+    <t>47656024</t>
+  </si>
+  <si>
+    <t>00444615</t>
+  </si>
+  <si>
+    <t>44164626</t>
+  </si>
+  <si>
+    <t>10576320</t>
+  </si>
+  <si>
+    <t>73593686</t>
+  </si>
+  <si>
+    <t>41138839</t>
+  </si>
+  <si>
+    <t>41297310</t>
+  </si>
+  <si>
     <t>AGUIRRE CARRASCAL CARLOS ENRIQUE</t>
   </si>
   <si>
@@ -503,6 +906,36 @@
     <t>ZUÑIGA CAMA MANUEL EDUARDO</t>
   </si>
   <si>
+    <t>40362968</t>
+  </si>
+  <si>
+    <t>24687727</t>
+  </si>
+  <si>
+    <t>44025677</t>
+  </si>
+  <si>
+    <t>42252434</t>
+  </si>
+  <si>
+    <t>42431271</t>
+  </si>
+  <si>
+    <t>40434746</t>
+  </si>
+  <si>
+    <t>76834183</t>
+  </si>
+  <si>
+    <t>71932329</t>
+  </si>
+  <si>
+    <t>02550498</t>
+  </si>
+  <si>
+    <t>70355875</t>
+  </si>
+  <si>
     <t>AREVALO DE LA ROCA JUAN CARLOS</t>
   </si>
   <si>
@@ -540,22 +973,20 @@
   </si>
   <si>
     <t>VILLARROEL LOPEZ LUIS KAROL</t>
+  </si>
+  <si>
+    <t>70558966</t>
+  </si>
+  <si>
+    <t>LUIS CHACHI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -583,16 +1014,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -927,1341 +1356,1347 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD330490-A8A1-49E3-86FF-A6622C7A89BB}">
-  <dimension ref="A1:H166"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <dimension ref="A1:B167"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="45.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.19921875" style="2"/>
+    <col min="2" max="2" width="45.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="3">
-        <v>9874967</v>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="3">
-        <v>409316</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="3">
-        <v>10604841</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="3">
-        <v>10108517</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="3">
-        <v>10264107</v>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="3">
-        <v>48716409</v>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="3">
-        <v>74574889</v>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="3">
-        <v>1991139</v>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="3">
-        <v>73386474</v>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="3">
-        <v>70367111</v>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
         <v>40752658</v>
       </c>
       <c r="B12" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="3">
-        <v>2546314</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="3">
-        <v>32980742</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="3">
-        <v>43728469</v>
-      </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="3">
-        <v>24494456</v>
-      </c>
-      <c r="B16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="3">
-        <v>41004089</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="3">
-        <v>40303753</v>
-      </c>
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-    </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="3">
-        <v>47906470</v>
+      <c r="A19" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="3">
-        <v>40896187</v>
+      <c r="A20" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="3">
-        <v>9963107</v>
+      <c r="A21" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="3">
+      <c r="A22" s="2">
         <v>70295470</v>
       </c>
       <c r="B22" t="s">
-        <v>155</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="3">
-        <v>41137298</v>
+      <c r="A23" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="3">
-        <v>29631887</v>
+      <c r="A24" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="3">
-        <v>40974286</v>
+      <c r="A25" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="3">
-        <v>20440891</v>
+      <c r="A26" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="3">
-        <v>42950740</v>
+      <c r="A27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="3">
-        <v>23996183</v>
+      <c r="A28" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="3">
-        <v>40409818</v>
+      <c r="A29" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="3">
-        <v>1539176</v>
+      <c r="A30" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="3">
+      <c r="A31" s="2">
         <v>71831646</v>
       </c>
       <c r="B31" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="3">
-        <v>75716072</v>
-      </c>
       <c r="B32" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="3">
-        <v>29547818</v>
-      </c>
       <c r="B33" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B34" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="3">
-        <v>40362968</v>
-      </c>
-      <c r="B34" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="3">
-        <v>28714683</v>
-      </c>
       <c r="B35" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="3">
-        <v>43952255</v>
-      </c>
       <c r="B36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="3">
-        <v>2044816</v>
-      </c>
       <c r="B37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="3">
-        <v>20068854</v>
-      </c>
       <c r="B38" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B39" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="3">
-        <v>24687727</v>
-      </c>
-      <c r="B39" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="3">
-        <v>42177491</v>
-      </c>
       <c r="B40" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="3">
-        <v>43548231</v>
-      </c>
       <c r="B41" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="3">
-        <v>23274872</v>
-      </c>
       <c r="B42" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B43" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="3">
-        <v>44025677</v>
-      </c>
-      <c r="B43" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="3">
-        <v>75102983</v>
-      </c>
       <c r="B44" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="3">
-        <v>80064592</v>
-      </c>
       <c r="B45" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="3">
-        <v>47590083</v>
-      </c>
       <c r="B46" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="3">
-        <v>41648714</v>
-      </c>
       <c r="B47" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="3">
-        <v>1298035</v>
-      </c>
       <c r="B48" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="3">
-        <v>40604738</v>
-      </c>
       <c r="B49" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="3">
-        <v>40329505</v>
-      </c>
       <c r="B50" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="3">
-        <v>44235236</v>
-      </c>
       <c r="B51" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="3">
-        <v>72019595</v>
-      </c>
       <c r="B52" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="3">
-        <v>41968733</v>
-      </c>
       <c r="B53" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="3">
-        <v>80317947</v>
-      </c>
       <c r="B54" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="3">
-        <v>42966692</v>
-      </c>
       <c r="B55" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="3">
-        <v>2542365</v>
-      </c>
       <c r="B56" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B57" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="3">
-        <v>42252434</v>
-      </c>
-      <c r="B57" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="3">
-        <v>43958280</v>
-      </c>
       <c r="B58" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="3">
-        <v>44275274</v>
-      </c>
       <c r="B59" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="3">
-        <v>45089074</v>
-      </c>
       <c r="B60" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="3">
-        <v>28274549</v>
-      </c>
       <c r="B61" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="3">
-        <v>41672593</v>
-      </c>
       <c r="B62" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="3">
-        <v>42725445</v>
-      </c>
       <c r="B63" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="3">
-        <v>24698674</v>
-      </c>
       <c r="B64" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="3">
-        <v>73598701</v>
-      </c>
       <c r="B65" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="2">
+        <v>31677451</v>
+      </c>
+      <c r="B66" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="3">
-        <v>31677451</v>
-      </c>
-      <c r="B66" t="s">
+      <c r="B67" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="3">
-        <v>80533325</v>
-      </c>
-      <c r="B67" t="s">
+      <c r="B68" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="3">
-        <v>47800527</v>
-      </c>
-      <c r="B68" t="s">
+      <c r="B69" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B70" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="3">
-        <v>47399870</v>
-      </c>
-      <c r="B69" t="s">
+      <c r="B71" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B72" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="3">
-        <v>42431271</v>
-      </c>
-      <c r="B70" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="3">
-        <v>45384441</v>
-      </c>
-      <c r="B71" t="s">
+      <c r="B73" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="3">
-        <v>40434746</v>
-      </c>
-      <c r="B72" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="3">
-        <v>46513926</v>
-      </c>
-      <c r="B73" t="s">
+      <c r="B74" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="3">
-        <v>8769965</v>
-      </c>
-      <c r="B74" t="s">
+      <c r="B75" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="2">
+        <v>42305005</v>
+      </c>
+      <c r="B76" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="3">
-        <v>44352393</v>
-      </c>
-      <c r="B75" t="s">
+      <c r="B77" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="3">
-        <v>42305005</v>
-      </c>
-      <c r="B76" t="s">
+      <c r="B78" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="3">
-        <v>40947821</v>
-      </c>
-      <c r="B77" t="s">
+      <c r="B79" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="3">
-        <v>9244927</v>
-      </c>
-      <c r="B78" t="s">
+      <c r="B80" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="2">
+        <v>46881401</v>
+      </c>
+      <c r="B81" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="3">
-        <v>47595131</v>
-      </c>
-      <c r="B79" t="s">
+      <c r="B82" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="3">
-        <v>71019123</v>
-      </c>
-      <c r="B80" t="s">
+      <c r="B83" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="2">
+        <v>41996873</v>
+      </c>
+      <c r="B84" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="3">
-        <v>46881401</v>
-      </c>
-      <c r="B81" t="s">
+      <c r="B85" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="3">
-        <v>10727102</v>
-      </c>
-      <c r="B82" t="s">
+      <c r="B86" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="3">
-        <v>6808878</v>
-      </c>
-      <c r="B83" t="s">
+      <c r="B87" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="3">
-        <v>41996873</v>
-      </c>
-      <c r="B84" t="s">
+      <c r="B88" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="3">
-        <v>48619119</v>
-      </c>
-      <c r="B85" t="s">
+      <c r="B89" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="3">
-        <v>70013083</v>
-      </c>
-      <c r="B86" t="s">
+      <c r="B90" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="3">
-        <v>40891715</v>
-      </c>
-      <c r="B87" t="s">
+      <c r="B91" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="2">
+        <v>20427241</v>
+      </c>
+      <c r="B92" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="3">
-        <v>70417820</v>
-      </c>
-      <c r="B88" t="s">
+      <c r="B93" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="2">
+        <v>46217452</v>
+      </c>
+      <c r="B94" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="3">
-        <v>43973895</v>
-      </c>
-      <c r="B89" t="s">
+      <c r="B95" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="3">
-        <v>73415532</v>
-      </c>
-      <c r="B90" t="s">
+      <c r="B96" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="3">
-        <v>74574874</v>
-      </c>
-      <c r="B91" t="s">
+      <c r="B97" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E91" s="2"/>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="3">
-        <v>20427241</v>
-      </c>
-      <c r="B92" t="s">
+      <c r="B98" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E92" s="2"/>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="3">
-        <v>43032559</v>
-      </c>
-      <c r="B93" t="s">
+      <c r="B99" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B100" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="3">
-        <v>46217452</v>
-      </c>
-      <c r="B94" t="s">
+      <c r="B101" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="3">
-        <v>44241105</v>
-      </c>
-      <c r="B95" t="s">
+      <c r="B102" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="3">
-        <v>80569866</v>
-      </c>
-      <c r="B96" t="s">
+      <c r="B103" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" s="3">
-        <v>2553630</v>
-      </c>
-      <c r="B97" t="s">
+      <c r="B104" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" s="3">
-        <v>41997576</v>
-      </c>
-      <c r="B98" t="s">
+      <c r="B105" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B106" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" s="3">
-        <v>61195518</v>
-      </c>
-      <c r="B99" t="s">
+      <c r="B107" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="3">
-        <v>76834183</v>
-      </c>
-      <c r="B100" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" s="3">
-        <v>676531</v>
-      </c>
-      <c r="B101" t="s">
+      <c r="B108" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" s="3">
-        <v>40662325</v>
-      </c>
-      <c r="B102" t="s">
+      <c r="B109" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" s="3">
-        <v>2425316</v>
-      </c>
-      <c r="B103" t="s">
+      <c r="B110" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B111" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="3">
-        <v>73304687</v>
-      </c>
-      <c r="B104" t="s">
+      <c r="B112" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" s="3">
-        <v>10070171</v>
-      </c>
-      <c r="B105" t="s">
+      <c r="B113" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" s="3">
-        <v>71932329</v>
-      </c>
-      <c r="B106" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" s="3">
-        <v>46219653</v>
-      </c>
-      <c r="B107" t="s">
+      <c r="B114" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>60820639</v>
+      </c>
+      <c r="B115" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" s="3">
-        <v>30766789</v>
-      </c>
-      <c r="B108" t="s">
+      <c r="B116" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109" s="3">
-        <v>31662709</v>
-      </c>
-      <c r="B109" t="s">
+      <c r="B117" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110" s="3">
-        <v>43769088</v>
-      </c>
-      <c r="B110" t="s">
+      <c r="B118" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" s="3">
-        <v>2550498</v>
-      </c>
-      <c r="B111" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" s="3">
-        <v>40324519</v>
-      </c>
-      <c r="B112" t="s">
+      <c r="B119" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="3">
-        <v>46361156</v>
-      </c>
-      <c r="B113" t="s">
+      <c r="B120" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="3">
-        <v>80548721</v>
-      </c>
-      <c r="B114" t="s">
+      <c r="B121" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="3">
-        <v>60820639</v>
-      </c>
-      <c r="B115" t="s">
+      <c r="B122" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="3">
-        <v>71333124</v>
-      </c>
-      <c r="B116" t="s">
+      <c r="B123" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="3">
-        <v>42036243</v>
-      </c>
-      <c r="B117" t="s">
+      <c r="B124" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" s="3">
-        <v>71790593</v>
-      </c>
-      <c r="B118" t="s">
+      <c r="B125" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" s="3">
-        <v>43700994</v>
-      </c>
-      <c r="B119" t="s">
+      <c r="B126" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" s="3">
-        <v>1332505</v>
-      </c>
-      <c r="B120" t="s">
+      <c r="B127" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" s="3">
-        <v>4743900</v>
-      </c>
-      <c r="B121" t="s">
+      <c r="B128" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>43539336</v>
+      </c>
+      <c r="B129" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" s="3">
-        <v>46912053</v>
-      </c>
-      <c r="B122" t="s">
+      <c r="B130" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123" s="3">
-        <v>70768801</v>
-      </c>
-      <c r="B123" t="s">
+      <c r="B131" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" s="3">
-        <v>75972848</v>
-      </c>
-      <c r="B124" t="s">
+      <c r="B132" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>31601357</v>
+      </c>
+      <c r="B133" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125" s="3">
-        <v>47056207</v>
-      </c>
-      <c r="B125" t="s">
+      <c r="B134" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" s="3">
-        <v>28281963</v>
-      </c>
-      <c r="B126" t="s">
+      <c r="B135" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" s="3">
-        <v>46766546</v>
-      </c>
-      <c r="B127" t="s">
+      <c r="B136" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128" s="3">
-        <v>42535729</v>
-      </c>
-      <c r="B128" t="s">
+      <c r="B137" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="3">
-        <v>43539336</v>
-      </c>
-      <c r="B129" t="s">
+      <c r="B138" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>40052591</v>
+      </c>
+      <c r="B139" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="3">
-        <v>42656588</v>
-      </c>
-      <c r="B130" t="s">
+      <c r="B140" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B141" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="3">
-        <v>29725729</v>
-      </c>
-      <c r="B131" t="s">
+      <c r="B142" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="3">
-        <v>40203991</v>
-      </c>
-      <c r="B132" t="s">
+      <c r="B143" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>40782264</v>
+      </c>
+      <c r="B144" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>76465704</v>
+      </c>
+      <c r="B145" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="3">
-        <v>31601357</v>
-      </c>
-      <c r="B133" t="s">
+      <c r="B146" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" s="3">
-        <v>40229371</v>
-      </c>
-      <c r="B134" t="s">
+      <c r="B147" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" s="3">
-        <v>47604404</v>
-      </c>
-      <c r="B135" t="s">
+      <c r="B148" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>10663914</v>
+      </c>
+      <c r="B149" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" s="3">
-        <v>2527553</v>
-      </c>
-      <c r="B136" t="s">
+      <c r="B150" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" s="3">
-        <v>72709468</v>
-      </c>
-      <c r="B137" t="s">
+      <c r="B151" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" s="3">
-        <v>41586331</v>
-      </c>
-      <c r="B138" t="s">
+      <c r="B152" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>42198740</v>
+      </c>
+      <c r="B153" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" s="3">
-        <v>40052591</v>
-      </c>
-      <c r="B139" t="s">
+      <c r="B154" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" s="3">
-        <v>72251136</v>
-      </c>
-      <c r="B140" t="s">
+      <c r="B155" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" s="3">
-        <v>70355875</v>
-      </c>
-      <c r="B141" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" s="3">
-        <v>73547288</v>
-      </c>
-      <c r="B142" t="s">
+      <c r="B156" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="143" spans="1:2">
-      <c r="A143" s="3">
-        <v>44978131</v>
-      </c>
-      <c r="B143" t="s">
+      <c r="B157" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="3">
-        <v>40782264</v>
-      </c>
-      <c r="B144" t="s">
+      <c r="B158" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="3">
-        <v>76465704</v>
-      </c>
-      <c r="B145" t="s">
+      <c r="B159" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="3">
-        <v>46265351</v>
-      </c>
-      <c r="B146" t="s">
+      <c r="B160" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" s="3">
-        <v>48149851</v>
-      </c>
-      <c r="B147" t="s">
+      <c r="B161" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>43928099</v>
+      </c>
+      <c r="B162" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="3">
-        <v>2545100</v>
-      </c>
-      <c r="B148" t="s">
+      <c r="B163" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="3">
-        <v>10663914</v>
-      </c>
-      <c r="B149" t="s">
+      <c r="B164" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="3">
-        <v>75021649</v>
-      </c>
-      <c r="B150" t="s">
+      <c r="B165" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" s="3">
-        <v>42492796</v>
-      </c>
-      <c r="B151" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="3">
-        <v>80113798</v>
-      </c>
-      <c r="B152" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" s="3">
-        <v>42198740</v>
-      </c>
-      <c r="B153" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" s="3">
-        <v>74497311</v>
-      </c>
-      <c r="B154" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="3">
-        <v>5958276</v>
-      </c>
-      <c r="B155" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" s="3">
-        <v>47037763</v>
-      </c>
-      <c r="B156" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="3">
-        <v>42972864</v>
-      </c>
-      <c r="B157" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="3">
-        <v>41445238</v>
-      </c>
-      <c r="B158" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="3">
-        <v>47656024</v>
-      </c>
-      <c r="B159" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" s="4">
-        <v>444615</v>
-      </c>
-      <c r="B160" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="4">
-        <v>44164626</v>
-      </c>
-      <c r="B161" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="4">
-        <v>43928099</v>
-      </c>
-      <c r="B162" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" s="4">
-        <v>10576320</v>
-      </c>
-      <c r="B163" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="4">
-        <v>73593686</v>
-      </c>
-      <c r="B164" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="4">
-        <v>41138839</v>
-      </c>
-      <c r="B165" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="4">
-        <v>41297310</v>
-      </c>
       <c r="B166" t="s">
-        <v>153</v>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B167" t="s">
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7CA2527-D1CC-47CC-AB67-E8D069B96124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447930C8-5C1D-44CD-A708-7075E0C977EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="96" yWindow="0" windowWidth="14868" windowHeight="12240" xr2:uid="{878F31C5-4CEA-4304-87C5-39FC92D222CB}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="318">
   <si>
     <t>DNI</t>
   </si>
@@ -979,6 +979,12 @@
   </si>
   <si>
     <t>LUIS CHACHI</t>
+  </si>
+  <si>
+    <t>KARLA PACHECO</t>
+  </si>
+  <si>
+    <t>71295471</t>
   </si>
 </sst>
 </file>
@@ -1356,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD330490-A8A1-49E3-86FF-A6622C7A89BB}">
-  <dimension ref="A1:B167"/>
+  <dimension ref="A1:B168"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="2"/>
@@ -2699,6 +2705,14 @@
         <v>315</v>
       </c>
     </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B168" t="s">
+        <v>316</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447930C8-5C1D-44CD-A708-7075E0C977EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F61E538-2FEC-42B6-A091-F8A22CD9B7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="96" yWindow="0" windowWidth="14868" windowHeight="12240" xr2:uid="{878F31C5-4CEA-4304-87C5-39FC92D222CB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{878F31C5-4CEA-4304-87C5-39FC92D222CB}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="361">
   <si>
     <t>DNI</t>
   </si>
@@ -54,9 +54,6 @@
     <t>10264107</t>
   </si>
   <si>
-    <t>48716409</t>
-  </si>
-  <si>
     <t>74574889</t>
   </si>
   <si>
@@ -126,9 +123,6 @@
     <t>29547818</t>
   </si>
   <si>
-    <t>28714683</t>
-  </si>
-  <si>
     <t>43952255</t>
   </si>
   <si>
@@ -189,9 +183,6 @@
     <t>43958280</t>
   </si>
   <si>
-    <t>44275274</t>
-  </si>
-  <si>
     <t>45089074</t>
   </si>
   <si>
@@ -276,9 +267,6 @@
     <t>44241105</t>
   </si>
   <si>
-    <t>80569866</t>
-  </si>
-  <si>
     <t>02553630</t>
   </si>
   <si>
@@ -324,9 +312,6 @@
     <t>80548721</t>
   </si>
   <si>
-    <t>71333124</t>
-  </si>
-  <si>
     <t>42036243</t>
   </si>
   <si>
@@ -372,18 +357,12 @@
     <t>40203991</t>
   </si>
   <si>
-    <t>40229371</t>
-  </si>
-  <si>
     <t>47604404</t>
   </si>
   <si>
     <t>02527553</t>
   </si>
   <si>
-    <t>72709468</t>
-  </si>
-  <si>
     <t>41586331</t>
   </si>
   <si>
@@ -465,9 +444,6 @@
     <t>ALVARADO BRAVO CANCION BERNARDO</t>
   </si>
   <si>
-    <t>AÑAMURO MAMANI ROGER</t>
-  </si>
-  <si>
     <t>APAZA LARICO BISMARCK</t>
   </si>
   <si>
@@ -540,9 +516,6 @@
     <t>CHANCAYAURI VALERO ALBERTO</t>
   </si>
   <si>
-    <t>CHAVEZ TAMBRACC JUAN</t>
-  </si>
-  <si>
     <t>CHIPANA MACHACA TONY WILLIAN</t>
   </si>
   <si>
@@ -603,9 +576,6 @@
     <t>GOMEZ VICHATA JORGE</t>
   </si>
   <si>
-    <t>GRIJALVA BAJALQUE ARNOLD JUNIOR</t>
-  </si>
-  <si>
     <t>GUEVARA COTRINA JORGE HECTOR</t>
   </si>
   <si>
@@ -708,9 +678,6 @@
     <t>MAMANI ARRAYA DAVID EDISON</t>
   </si>
   <si>
-    <t>MAMANI AYALA, LUCIANO</t>
-  </si>
-  <si>
     <t>MAMANI CCORI NESTOR</t>
   </si>
   <si>
@@ -759,9 +726,6 @@
     <t>PADILLA VARGAS ABNER</t>
   </si>
   <si>
-    <t>PALACIOS DE LA CRUZ ERICK CRISTIAN</t>
-  </si>
-  <si>
     <t>PAREDES MELGAR FERNANDO NICANOR</t>
   </si>
   <si>
@@ -813,18 +777,12 @@
     <t>RAMIREZ CORDOVA NARCISO ALEJANDRO</t>
   </si>
   <si>
-    <t>RAMOS RAMOS JULIO</t>
-  </si>
-  <si>
     <t>RAMOS TICONA EDWIN YONI</t>
   </si>
   <si>
     <t>RAMOS VILLALBA DEMETRIO CALIXTO</t>
   </si>
   <si>
-    <t>REYES LOARTE BRITHZA NATHALY</t>
-  </si>
-  <si>
     <t>RIVERA HUAYHUA WILDER ALFREDO</t>
   </si>
   <si>
@@ -912,12 +870,6 @@
     <t>24687727</t>
   </si>
   <si>
-    <t>44025677</t>
-  </si>
-  <si>
-    <t>42252434</t>
-  </si>
-  <si>
     <t>42431271</t>
   </si>
   <si>
@@ -948,12 +900,6 @@
     <t>CHUNGA QUINCHO ALFREDO</t>
   </si>
   <si>
-    <t>CORDOVA NORABUENA HITLER</t>
-  </si>
-  <si>
-    <t>GIL ENCISO DEIVIS RAFAEL</t>
-  </si>
-  <si>
     <t>HUANACUNI CHOQUE GENARO WALTER</t>
   </si>
   <si>
@@ -975,16 +921,199 @@
     <t>VILLARROEL LOPEZ LUIS KAROL</t>
   </si>
   <si>
-    <t>70558966</t>
-  </si>
-  <si>
-    <t>LUIS CHACHI</t>
-  </si>
-  <si>
-    <t>KARLA PACHECO</t>
-  </si>
-  <si>
-    <t>71295471</t>
+    <t>62080184</t>
+  </si>
+  <si>
+    <t>23012517</t>
+  </si>
+  <si>
+    <t>29592403</t>
+  </si>
+  <si>
+    <t>80617977</t>
+  </si>
+  <si>
+    <t>43354084</t>
+  </si>
+  <si>
+    <t>76096435</t>
+  </si>
+  <si>
+    <t>42934793</t>
+  </si>
+  <si>
+    <t>80199159</t>
+  </si>
+  <si>
+    <t>02415430</t>
+  </si>
+  <si>
+    <t>80495492</t>
+  </si>
+  <si>
+    <t>28275688</t>
+  </si>
+  <si>
+    <t>44208704</t>
+  </si>
+  <si>
+    <t>24716362</t>
+  </si>
+  <si>
+    <t>73651334</t>
+  </si>
+  <si>
+    <t>73819477</t>
+  </si>
+  <si>
+    <t>02400679</t>
+  </si>
+  <si>
+    <t>42246125</t>
+  </si>
+  <si>
+    <t>40040184</t>
+  </si>
+  <si>
+    <t>46596554</t>
+  </si>
+  <si>
+    <t>04651038</t>
+  </si>
+  <si>
+    <t>01325351</t>
+  </si>
+  <si>
+    <t>60176663</t>
+  </si>
+  <si>
+    <t>46152948</t>
+  </si>
+  <si>
+    <t>44959881</t>
+  </si>
+  <si>
+    <t>46331842</t>
+  </si>
+  <si>
+    <t>80636888</t>
+  </si>
+  <si>
+    <t>CABANILLAS ALVITES ALDAIR</t>
+  </si>
+  <si>
+    <t>CADILLO PALACIOS CARLOS</t>
+  </si>
+  <si>
+    <t>CALCINA HUAMAN VICENTE MODESTO</t>
+  </si>
+  <si>
+    <t>CALLO CALLO EDILBERTO</t>
+  </si>
+  <si>
+    <t>CARDENAS CONDOLI JUAN</t>
+  </si>
+  <si>
+    <t>CASA HUILLCA ISAI JONAS</t>
+  </si>
+  <si>
+    <t>CCOAQUIRA QUISPE AVELINO</t>
+  </si>
+  <si>
+    <t>CERVANTES HUERTA AMADOR</t>
+  </si>
+  <si>
+    <t>CHOQUITARQUE MACEDO RAUL</t>
+  </si>
+  <si>
+    <t>COLQUEHUANCA LIMA ABEL</t>
+  </si>
+  <si>
+    <t>CONDORI COSI ANSELMO</t>
+  </si>
+  <si>
+    <t>ESPINOZA CARPIO MILTON</t>
+  </si>
+  <si>
+    <t>GUERRERO PEÑA EDGAR GERMAN</t>
+  </si>
+  <si>
+    <t>GUZMAN HINOSTROZA VICTOR</t>
+  </si>
+  <si>
+    <t>LAVERIANO PALOMINO DAVID OLIVER</t>
+  </si>
+  <si>
+    <t>LISBOA GONCALVES MILTON ANDRE</t>
+  </si>
+  <si>
+    <t>MAMANI ARONI SATURNINO DEMETRIO</t>
+  </si>
+  <si>
+    <t>MAMANI OCHOA NICOL ANEL</t>
+  </si>
+  <si>
+    <t>MAMANI SUMERINDE LIZ</t>
+  </si>
+  <si>
+    <t>MARIN FIGUEROA JUAN BAUTISTA</t>
+  </si>
+  <si>
+    <t>MASIAS SALDIVAR AMILCAR</t>
+  </si>
+  <si>
+    <t>MILLAN QUINTANILLA JHOEL</t>
+  </si>
+  <si>
+    <t>MONCADA CALISAYA BONIFACIO</t>
+  </si>
+  <si>
+    <t>MUÑOZ PERALTA HUGO EDGAR</t>
+  </si>
+  <si>
+    <t>MUÑOZ VILLACORTA ROMARIO</t>
+  </si>
+  <si>
+    <t>PALOMINO DELGADILLO ESTEFANY HEYDI</t>
+  </si>
+  <si>
+    <t>PANOCA ALANIA RUYER EDGARDO</t>
+  </si>
+  <si>
+    <t>PARISUAÑA HUACASI FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>PORRAS QUIJADA ELVIS IVAN</t>
+  </si>
+  <si>
+    <t>QUISPE CHOQUETICO JHAROL TEOFILO</t>
+  </si>
+  <si>
+    <t>QUISPE HUYHUA ALBERTO</t>
+  </si>
+  <si>
+    <t>RAMOS GARCIA ESWIN ESMIT</t>
+  </si>
+  <si>
+    <t>RAMOS ÑAHUI HERMILIO FREDY</t>
+  </si>
+  <si>
+    <t>SAMAN CACERES WILBERT SANDRO</t>
+  </si>
+  <si>
+    <t>SANCHO TORRES JAMILTON ROLAND</t>
+  </si>
+  <si>
+    <t>TORRICO JUAREZ MARCIAL</t>
+  </si>
+  <si>
+    <t>VALENTINE SAUSA FABRICIO ANDRE</t>
+  </si>
+  <si>
+    <t>VELIZ COLQUE MARIBEL</t>
+  </si>
+  <si>
+    <t>VILLANUEVA CARBAJAL JUAN CARLOS</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1028,6 +1157,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1362,7 +1492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD330490-A8A1-49E3-86FF-A6622C7A89BB}">
-  <dimension ref="A1:B168"/>
+  <dimension ref="A1:B196"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="2"/>
@@ -1381,1336 +1511,1560 @@
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>139</v>
+      <c r="B2" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>140</v>
+      <c r="B3" s="3" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
-        <v>141</v>
+      <c r="B4" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
-        <v>142</v>
+      <c r="B5" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
-        <v>143</v>
+      <c r="B6" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
-        <v>144</v>
+      <c r="B7" s="3" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
-        <v>145</v>
+      <c r="B8" s="3" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
-        <v>146</v>
+      <c r="B9" s="3" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
-        <v>147</v>
+      <c r="B10" s="3" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="2">
+        <v>40752658</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="2">
-        <v>40752658</v>
-      </c>
-      <c r="B12" t="s">
-        <v>301</v>
+      <c r="B12" s="3" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>149</v>
+      <c r="B13" s="3" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>150</v>
+      <c r="B14" s="3" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>151</v>
+      <c r="B15" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>152</v>
+      <c r="B16" s="3" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>153</v>
+      <c r="B17" s="3" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>154</v>
+      <c r="B18" s="3" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>155</v>
+      <c r="B19" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>156</v>
+      <c r="B20" s="3" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>157</v>
+      <c r="A21" s="2">
+        <v>70295470</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="2">
-        <v>70295470</v>
-      </c>
-      <c r="B22" t="s">
-        <v>302</v>
+      <c r="A22" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>158</v>
+        <v>297</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>159</v>
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>160</v>
+        <v>298</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" t="s">
-        <v>161</v>
+        <v>21</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" t="s">
-        <v>162</v>
+        <v>22</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" t="s">
-        <v>163</v>
+        <v>299</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
-        <v>164</v>
+        <v>23</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" t="s">
-        <v>165</v>
+        <v>300</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="2">
-        <v>71831646</v>
-      </c>
-      <c r="B31" t="s">
-        <v>166</v>
+      <c r="A31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" t="s">
-        <v>167</v>
+        <v>301</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" t="s">
-        <v>168</v>
+        <v>25</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B34" t="s">
-        <v>303</v>
+        <v>26</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" t="s">
-        <v>169</v>
+      <c r="A35" s="2">
+        <v>24006626</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36" t="s">
-        <v>170</v>
+        <v>302</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B37" t="s">
-        <v>171</v>
+        <v>27</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38" t="s">
-        <v>172</v>
+      <c r="A38" s="2">
+        <v>71831646</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="B39" t="s">
-        <v>304</v>
+        <v>28</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" t="s">
-        <v>173</v>
+        <v>29</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41" t="s">
-        <v>174</v>
+        <v>277</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" t="s">
-        <v>175</v>
+        <v>30</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="B43" t="s">
-        <v>305</v>
+        <v>31</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" t="s">
-        <v>176</v>
+      <c r="A44" s="2">
+        <v>46218602</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" t="s">
-        <v>177</v>
+        <v>32</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" t="s">
-        <v>178</v>
+        <v>278</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" t="s">
-        <v>179</v>
+        <v>33</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" t="s">
-        <v>180</v>
+        <v>303</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" t="s">
-        <v>181</v>
+        <v>304</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" t="s">
-        <v>182</v>
+        <v>34</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" t="s">
-        <v>183</v>
+        <v>35</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" t="s">
-        <v>184</v>
+        <v>36</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53" t="s">
-        <v>185</v>
+        <v>37</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B54" t="s">
-        <v>186</v>
+        <v>38</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B55" t="s">
-        <v>187</v>
+        <v>39</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B56" t="s">
-        <v>188</v>
+        <v>40</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="B57" t="s">
-        <v>306</v>
+        <v>41</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B58" t="s">
-        <v>189</v>
+        <v>42</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B59" t="s">
-        <v>190</v>
+        <v>43</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B60" t="s">
-        <v>191</v>
+        <v>44</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B61" t="s">
-        <v>192</v>
+        <v>305</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B62" t="s">
-        <v>193</v>
+        <v>45</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B63" t="s">
-        <v>194</v>
+        <v>46</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B64" t="s">
-        <v>195</v>
+        <v>47</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B65" t="s">
-        <v>196</v>
+        <v>48</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="2">
-        <v>31677451</v>
-      </c>
-      <c r="B66" t="s">
-        <v>197</v>
+      <c r="A66" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" t="s">
-        <v>198</v>
+      <c r="A67" s="2">
+        <v>15743938</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B68" t="s">
-        <v>199</v>
+        <v>50</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B69" t="s">
-        <v>200</v>
+        <v>51</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B70" t="s">
-        <v>307</v>
+        <v>52</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B71" t="s">
-        <v>201</v>
+        <v>53</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="B72" t="s">
-        <v>308</v>
+        <v>54</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B73" t="s">
-        <v>202</v>
+        <v>55</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B74" t="s">
-        <v>203</v>
+        <v>306</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75" t="s">
-        <v>204</v>
+      <c r="A75" s="2">
+        <v>31677451</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="2">
-        <v>42305005</v>
-      </c>
-      <c r="B76" t="s">
-        <v>205</v>
+      <c r="A76" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B77" t="s">
-        <v>206</v>
+        <v>57</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B78" t="s">
-        <v>207</v>
+        <v>58</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B79" t="s">
-        <v>208</v>
+        <v>279</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B80" t="s">
-        <v>209</v>
+        <v>59</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="2">
-        <v>46881401</v>
-      </c>
-      <c r="B81" t="s">
-        <v>210</v>
+      <c r="A81" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B82" t="s">
-        <v>211</v>
+        <v>60</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B83" t="s">
-        <v>212</v>
+        <v>61</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="2">
-        <v>41996873</v>
-      </c>
-      <c r="B84" t="s">
-        <v>213</v>
+      <c r="A84" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B85" t="s">
-        <v>214</v>
+      <c r="A85" s="2">
+        <v>42305005</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B86" t="s">
-        <v>215</v>
+        <v>63</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B87" t="s">
-        <v>216</v>
+        <v>64</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B88" t="s">
-        <v>217</v>
+        <v>65</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B89" t="s">
-        <v>218</v>
+        <v>66</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B90" t="s">
-        <v>219</v>
+      <c r="A90" s="2">
+        <v>46881401</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B91" t="s">
-        <v>220</v>
+        <v>307</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="2">
-        <v>20427241</v>
-      </c>
-      <c r="B92" t="s">
-        <v>221</v>
+      <c r="A92" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B93" t="s">
-        <v>222</v>
+        <v>68</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46217452</v>
-      </c>
-      <c r="B94" t="s">
-        <v>223</v>
+        <v>41996873</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B95" t="s">
-        <v>224</v>
+        <v>69</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B96" t="s">
-        <v>225</v>
+      <c r="A96" s="2">
+        <v>32882008</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B97" t="s">
-        <v>226</v>
+        <v>70</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B98" t="s">
-        <v>227</v>
+        <v>71</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B99" t="s">
-        <v>228</v>
+        <v>72</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="B100" t="s">
-        <v>309</v>
+        <v>73</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B101" t="s">
-        <v>229</v>
+        <v>74</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B102" t="s">
-        <v>230</v>
+        <v>75</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B103" t="s">
-        <v>231</v>
+      <c r="A103" s="2">
+        <v>20427241</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B104" t="s">
-        <v>232</v>
+        <v>76</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B105" t="s">
-        <v>233</v>
+      <c r="A105" s="2">
+        <v>46217452</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="B106" t="s">
-        <v>310</v>
+        <v>308</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B107" t="s">
-        <v>234</v>
+        <v>77</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B108" t="s">
-        <v>235</v>
+        <v>78</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B109" t="s">
-        <v>236</v>
+        <v>79</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B110" t="s">
-        <v>237</v>
+        <v>309</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="B111" t="s">
-        <v>311</v>
+        <v>80</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B112" t="s">
-        <v>238</v>
+        <v>281</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B113" t="s">
-        <v>239</v>
+        <v>81</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B114" t="s">
-        <v>240</v>
+        <v>310</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="2">
-        <v>60820639</v>
-      </c>
-      <c r="B115" t="s">
-        <v>241</v>
+      <c r="A115" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B116" t="s">
-        <v>242</v>
+        <v>311</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B117" t="s">
-        <v>243</v>
+        <v>312</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B118" t="s">
-        <v>244</v>
+        <v>83</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B119" t="s">
-        <v>245</v>
+        <v>84</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B120" t="s">
-        <v>246</v>
+        <v>85</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B121" t="s">
-        <v>247</v>
+        <v>282</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B122" t="s">
-        <v>248</v>
+      <c r="A122" s="2">
+        <v>10091490</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B123" t="s">
-        <v>249</v>
+        <v>86</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B124" t="s">
-        <v>250</v>
+        <v>313</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B125" t="s">
-        <v>251</v>
+        <v>87</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B126" t="s">
-        <v>252</v>
+        <v>88</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B127" t="s">
-        <v>253</v>
+      <c r="A127" s="2">
+        <v>26706595</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B128" t="s">
-        <v>254</v>
+        <v>314</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="2">
-        <v>43539336</v>
-      </c>
-      <c r="B129" t="s">
-        <v>255</v>
+      <c r="A129" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B130" t="s">
-        <v>256</v>
+        <v>283</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B131" t="s">
-        <v>257</v>
+        <v>90</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B132" t="s">
-        <v>258</v>
+        <v>91</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="2">
-        <v>31601357</v>
-      </c>
-      <c r="B133" t="s">
-        <v>259</v>
+      <c r="A133" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B134" t="s">
-        <v>260</v>
+      <c r="A134" s="2">
+        <v>60820639</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B135" t="s">
-        <v>261</v>
+      <c r="A135" s="2">
+        <v>76239928</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B136" t="s">
-        <v>262</v>
+        <v>315</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B137" t="s">
-        <v>263</v>
+        <v>93</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B138" t="s">
-        <v>264</v>
+        <v>94</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="2">
-        <v>40052591</v>
-      </c>
-      <c r="B139" t="s">
-        <v>265</v>
+      <c r="A139" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B140" t="s">
-        <v>266</v>
+        <v>95</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B141" t="s">
-        <v>312</v>
+        <v>96</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B142" t="s">
-        <v>267</v>
+        <v>97</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B143" t="s">
-        <v>268</v>
+        <v>98</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="2">
-        <v>40782264</v>
-      </c>
-      <c r="B144" t="s">
-        <v>269</v>
+      <c r="A144" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="2">
-        <v>76465704</v>
-      </c>
-      <c r="B145" t="s">
-        <v>270</v>
+      <c r="A145" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B146" t="s">
-        <v>271</v>
+        <v>101</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B147" t="s">
-        <v>272</v>
+        <v>102</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B148" t="s">
-        <v>273</v>
+        <v>103</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="2">
-        <v>10663914</v>
-      </c>
-      <c r="B149" t="s">
-        <v>274</v>
+      <c r="A149" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B150" t="s">
-        <v>275</v>
+      <c r="A150" s="2">
+        <v>43539336</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B151" t="s">
-        <v>276</v>
+      <c r="A151" s="2">
+        <v>10874713</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B152" t="s">
-        <v>277</v>
+        <v>105</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="2">
-        <v>42198740</v>
-      </c>
-      <c r="B153" t="s">
-        <v>278</v>
+      <c r="A153" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B154" t="s">
-        <v>279</v>
+        <v>317</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B155" t="s">
-        <v>280</v>
+        <v>107</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B156" t="s">
-        <v>281</v>
+      <c r="A156" s="2">
+        <v>28597752</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B157" t="s">
-        <v>282</v>
+      <c r="A157" s="2">
+        <v>31601357</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B158" t="s">
-        <v>283</v>
+      <c r="A158" s="2">
+        <v>70206733</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B159" t="s">
-        <v>284</v>
+        <v>318</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B160" t="s">
-        <v>285</v>
+        <v>108</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B161" t="s">
-        <v>286</v>
+        <v>109</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="2">
-        <v>43928099</v>
-      </c>
-      <c r="B162" t="s">
-        <v>313</v>
+      <c r="A162" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B163" t="s">
-        <v>287</v>
+      <c r="A163" s="2">
+        <v>40052591</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B164" t="s">
-        <v>288</v>
+        <v>111</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B165" t="s">
-        <v>289</v>
+        <v>284</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B166" t="s">
-        <v>290</v>
+        <v>112</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B167" t="s">
-        <v>315</v>
+        <v>113</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="B168" t="s">
-        <v>316</v>
+      <c r="A168" s="2">
+        <v>40105597</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>20659538</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>40782264</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>76465704</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>10663914</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>42198740</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>72637021</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>43928099</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F61E538-2FEC-42B6-A091-F8A22CD9B7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74A80E7-F440-4409-AC5A-14F0F3A8A08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{878F31C5-4CEA-4304-87C5-39FC92D222CB}"/>
   </bookViews>

--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D84BFDC-A85B-4308-B5C5-2FF68DEA4A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B07F285-74DD-4D04-9BDD-703FBFB5646C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{878F31C5-4CEA-4304-87C5-39FC92D222CB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{878F31C5-4CEA-4304-87C5-39FC92D222CB}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="447">
   <si>
     <t>DNI</t>
   </si>
@@ -114,9 +114,6 @@
     <t>CHALLCO ARQQUE NELIDA NANCY</t>
   </si>
   <si>
-    <t>CHAMPI AMAU WILFREDO</t>
-  </si>
-  <si>
     <t>CHANCAYAURI VALERO ALBERTO</t>
   </si>
   <si>
@@ -588,9 +585,6 @@
     <t>VELIZ COLQUE MARIBEL</t>
   </si>
   <si>
-    <t>VILLANUEVA CARBAJAL JUAN CARLOS</t>
-  </si>
-  <si>
     <t>GANOZA MARIN JOSE LUIS</t>
   </si>
   <si>
@@ -609,555 +603,9 @@
     <t>TTITO JUSTINIANI HECTOR</t>
   </si>
   <si>
-    <t>65044577</t>
-  </si>
-  <si>
-    <t>65044743</t>
-  </si>
-  <si>
-    <t>65040602</t>
-  </si>
-  <si>
-    <t>65046914</t>
-  </si>
-  <si>
-    <t>65028214</t>
-  </si>
-  <si>
-    <t>65035060</t>
-  </si>
-  <si>
-    <t>65044809</t>
-  </si>
-  <si>
-    <t>65044673</t>
-  </si>
-  <si>
-    <t>65045037</t>
-  </si>
-  <si>
-    <t>65044694</t>
-  </si>
-  <si>
-    <t>65044662</t>
-  </si>
-  <si>
-    <t>65020506</t>
-  </si>
-  <si>
-    <t>65024389</t>
-  </si>
-  <si>
-    <t>65016949</t>
-  </si>
-  <si>
-    <t>65035689</t>
-  </si>
-  <si>
-    <t>65000105</t>
-  </si>
-  <si>
-    <t>65040474</t>
-  </si>
-  <si>
-    <t>65039878</t>
-  </si>
-  <si>
-    <t>65013669</t>
-  </si>
-  <si>
-    <t>65046840</t>
-  </si>
-  <si>
-    <t>65035993</t>
-  </si>
-  <si>
-    <t>65002637</t>
-  </si>
-  <si>
-    <t>65044378</t>
-  </si>
-  <si>
-    <t>65012067</t>
-  </si>
-  <si>
-    <t>65044828</t>
-  </si>
-  <si>
-    <t>65040603</t>
-  </si>
-  <si>
-    <t>65045207</t>
-  </si>
-  <si>
-    <t>65038424</t>
-  </si>
-  <si>
-    <t>65034722</t>
-  </si>
-  <si>
-    <t>65046828</t>
-  </si>
-  <si>
-    <t>65010006</t>
-  </si>
-  <si>
-    <t>65034421</t>
-  </si>
-  <si>
-    <t>65046942</t>
-  </si>
-  <si>
-    <t>65041463</t>
-  </si>
-  <si>
-    <t>65035805</t>
-  </si>
-  <si>
-    <t>65002889</t>
-  </si>
-  <si>
-    <t>65040648</t>
-  </si>
-  <si>
-    <t>65044963</t>
-  </si>
-  <si>
-    <t>65046647</t>
-  </si>
-  <si>
-    <t>65043639</t>
-  </si>
-  <si>
-    <t>65015059</t>
-  </si>
-  <si>
-    <t>65038237</t>
-  </si>
-  <si>
-    <t>65046771</t>
-  </si>
-  <si>
-    <t>65045666</t>
-  </si>
-  <si>
-    <t>65038111</t>
-  </si>
-  <si>
-    <t>65001686</t>
-  </si>
-  <si>
-    <t>65045070</t>
-  </si>
-  <si>
-    <t>65000520</t>
-  </si>
-  <si>
-    <t>65046047</t>
-  </si>
-  <si>
-    <t>65021650</t>
-  </si>
-  <si>
-    <t>65023606</t>
-  </si>
-  <si>
-    <t>65000134</t>
-  </si>
-  <si>
-    <t>65030402</t>
-  </si>
-  <si>
-    <t>65042521</t>
-  </si>
-  <si>
-    <t>65044922</t>
-  </si>
-  <si>
-    <t>65041070</t>
-  </si>
-  <si>
-    <t>65046937</t>
-  </si>
-  <si>
-    <t>65025459</t>
-  </si>
-  <si>
-    <t>65046945</t>
-  </si>
-  <si>
-    <t>65015219</t>
-  </si>
-  <si>
-    <t>65028862</t>
-  </si>
-  <si>
-    <t>65046936</t>
-  </si>
-  <si>
-    <t>65045559</t>
-  </si>
-  <si>
-    <t>65046302</t>
-  </si>
-  <si>
-    <t>65043931</t>
-  </si>
-  <si>
-    <t>65046115</t>
-  </si>
-  <si>
-    <t>65004431</t>
-  </si>
-  <si>
-    <t>65030885</t>
-  </si>
-  <si>
-    <t>65002246</t>
-  </si>
-  <si>
-    <t>65008991</t>
-  </si>
-  <si>
-    <t>65046646</t>
-  </si>
-  <si>
-    <t>65040549</t>
-  </si>
-  <si>
-    <t>65046697</t>
-  </si>
-  <si>
-    <t>65044727</t>
-  </si>
-  <si>
-    <t>65041210</t>
-  </si>
-  <si>
-    <t>65028769</t>
-  </si>
-  <si>
-    <t>65046746</t>
-  </si>
-  <si>
-    <t>65036352</t>
-  </si>
-  <si>
-    <t>65044423</t>
-  </si>
-  <si>
-    <t>65007956</t>
-  </si>
-  <si>
-    <t>65006704</t>
-  </si>
-  <si>
-    <t>65002922</t>
-  </si>
-  <si>
-    <t>65041377</t>
-  </si>
-  <si>
-    <t>65044608</t>
-  </si>
-  <si>
-    <t>65039463</t>
-  </si>
-  <si>
-    <t>65043538</t>
-  </si>
-  <si>
-    <t>65008880</t>
-  </si>
-  <si>
-    <t>65044363</t>
-  </si>
-  <si>
-    <t>65045933</t>
-  </si>
-  <si>
-    <t>65044836</t>
-  </si>
-  <si>
-    <t>65044653</t>
-  </si>
-  <si>
-    <t>65035980</t>
-  </si>
-  <si>
-    <t>65011129</t>
-  </si>
-  <si>
-    <t>65033989</t>
-  </si>
-  <si>
-    <t>65046377</t>
-  </si>
-  <si>
-    <t>65044688</t>
-  </si>
-  <si>
-    <t>65046708</t>
-  </si>
-  <si>
-    <t>65044706</t>
-  </si>
-  <si>
-    <t>65013376</t>
-  </si>
-  <si>
-    <t>65044575</t>
-  </si>
-  <si>
-    <t>65044810</t>
-  </si>
-  <si>
-    <t>65044880</t>
-  </si>
-  <si>
-    <t>65046779</t>
-  </si>
-  <si>
-    <t>65044718</t>
-  </si>
-  <si>
-    <t>65046764</t>
-  </si>
-  <si>
-    <t>65036063</t>
-  </si>
-  <si>
-    <t>65046807</t>
-  </si>
-  <si>
-    <t>65046705</t>
-  </si>
-  <si>
-    <t>65046834</t>
-  </si>
-  <si>
-    <t>65046934</t>
-  </si>
-  <si>
-    <t>65046839</t>
-  </si>
-  <si>
-    <t>65044593</t>
-  </si>
-  <si>
-    <t>65044585</t>
-  </si>
-  <si>
-    <t>65046531</t>
-  </si>
-  <si>
-    <t>65039499</t>
-  </si>
-  <si>
-    <t>65046749</t>
-  </si>
-  <si>
-    <t>65044739</t>
-  </si>
-  <si>
-    <t>65046809</t>
-  </si>
-  <si>
-    <t>65045040</t>
-  </si>
-  <si>
-    <t>65000117</t>
-  </si>
-  <si>
-    <t>65045977</t>
-  </si>
-  <si>
-    <t>65043084</t>
-  </si>
-  <si>
-    <t>65046748</t>
-  </si>
-  <si>
-    <t>65038115</t>
-  </si>
-  <si>
-    <t>65030726</t>
-  </si>
-  <si>
-    <t>65013213</t>
-  </si>
-  <si>
-    <t>65040274</t>
-  </si>
-  <si>
-    <t>65029182</t>
-  </si>
-  <si>
-    <t>65044627</t>
-  </si>
-  <si>
-    <t>65035978</t>
-  </si>
-  <si>
-    <t>65046674</t>
-  </si>
-  <si>
-    <t>65046676</t>
-  </si>
-  <si>
-    <t>65046520</t>
-  </si>
-  <si>
-    <t>65044654</t>
-  </si>
-  <si>
-    <t>65038971</t>
-  </si>
-  <si>
-    <t>65013979</t>
-  </si>
-  <si>
-    <t>65046530</t>
-  </si>
-  <si>
-    <t>65043688</t>
-  </si>
-  <si>
-    <t>65031908</t>
-  </si>
-  <si>
-    <t>65006476</t>
-  </si>
-  <si>
-    <t>65046829</t>
-  </si>
-  <si>
-    <t>65032327</t>
-  </si>
-  <si>
-    <t>65000043</t>
-  </si>
-  <si>
-    <t>65040356</t>
-  </si>
-  <si>
-    <t>65034925</t>
-  </si>
-  <si>
-    <t>65039270</t>
-  </si>
-  <si>
-    <t>65045089</t>
-  </si>
-  <si>
-    <t>65044769</t>
-  </si>
-  <si>
-    <t>65033301</t>
-  </si>
-  <si>
-    <t>65003128</t>
-  </si>
-  <si>
-    <t>65044807</t>
-  </si>
-  <si>
-    <t>65044965</t>
-  </si>
-  <si>
-    <t>65038927</t>
-  </si>
-  <si>
-    <t>65040546</t>
-  </si>
-  <si>
-    <t>65025627</t>
-  </si>
-  <si>
-    <t>65046850</t>
-  </si>
-  <si>
-    <t>65046301</t>
-  </si>
-  <si>
-    <t>65040418</t>
-  </si>
-  <si>
-    <t>65046303</t>
-  </si>
-  <si>
-    <t>65044927</t>
-  </si>
-  <si>
-    <t>65039017</t>
-  </si>
-  <si>
-    <t>65044686</t>
-  </si>
-  <si>
-    <t>65044674</t>
-  </si>
-  <si>
-    <t>65002244</t>
-  </si>
-  <si>
-    <t>65044692</t>
-  </si>
-  <si>
-    <t>65046851</t>
-  </si>
-  <si>
-    <t>65046614</t>
-  </si>
-  <si>
-    <t>65043459</t>
-  </si>
-  <si>
-    <t>65043299</t>
-  </si>
-  <si>
-    <t>65033143</t>
-  </si>
-  <si>
-    <t>65006627</t>
-  </si>
-  <si>
-    <t>65043599</t>
-  </si>
-  <si>
-    <t>65012215</t>
-  </si>
-  <si>
-    <t>65046797</t>
-  </si>
-  <si>
-    <t>65039480</t>
-  </si>
-  <si>
-    <t>65046830</t>
-  </si>
-  <si>
-    <t>65001314</t>
-  </si>
-  <si>
-    <t>65046955</t>
-  </si>
-  <si>
-    <t>65046635</t>
-  </si>
-  <si>
-    <t>65046008</t>
-  </si>
-  <si>
-    <t>65046114</t>
-  </si>
-  <si>
     <t>ALCOSER HUAYTA YOEL</t>
   </si>
   <si>
-    <t>BELLIDO PADILLA ABEL</t>
-  </si>
-  <si>
     <t>CAPANI MATAMOROS WALTER</t>
   </si>
   <si>
@@ -1243,6 +691,687 @@
   </si>
   <si>
     <t>ZAPANA TURPO SUSY </t>
+  </si>
+  <si>
+    <t>09874967</t>
+  </si>
+  <si>
+    <t>00409316</t>
+  </si>
+  <si>
+    <t>10604841</t>
+  </si>
+  <si>
+    <t>44312995</t>
+  </si>
+  <si>
+    <t>10108517</t>
+  </si>
+  <si>
+    <t>10264107</t>
+  </si>
+  <si>
+    <t>74574889</t>
+  </si>
+  <si>
+    <t>46278187</t>
+  </si>
+  <si>
+    <t>01991139</t>
+  </si>
+  <si>
+    <t>73386474</t>
+  </si>
+  <si>
+    <t>70367111</t>
+  </si>
+  <si>
+    <t>02546314</t>
+  </si>
+  <si>
+    <t>32980742</t>
+  </si>
+  <si>
+    <t>40844695</t>
+  </si>
+  <si>
+    <t>48243054</t>
+  </si>
+  <si>
+    <t>43728469</t>
+  </si>
+  <si>
+    <t>24494456</t>
+  </si>
+  <si>
+    <t>41004089</t>
+  </si>
+  <si>
+    <t>40303753</t>
+  </si>
+  <si>
+    <t>47906470</t>
+  </si>
+  <si>
+    <t>40896187</t>
+  </si>
+  <si>
+    <t>27846337</t>
+  </si>
+  <si>
+    <t>09963107</t>
+  </si>
+  <si>
+    <t>62080184</t>
+  </si>
+  <si>
+    <t>46569896</t>
+  </si>
+  <si>
+    <t>23012517</t>
+  </si>
+  <si>
+    <t>41137298</t>
+  </si>
+  <si>
+    <t>29592403</t>
+  </si>
+  <si>
+    <t>29631887</t>
+  </si>
+  <si>
+    <t>40974286</t>
+  </si>
+  <si>
+    <t>44499928</t>
+  </si>
+  <si>
+    <t>43354084</t>
+  </si>
+  <si>
+    <t>71874993</t>
+  </si>
+  <si>
+    <t>42950740</t>
+  </si>
+  <si>
+    <t>76096435</t>
+  </si>
+  <si>
+    <t>44782033</t>
+  </si>
+  <si>
+    <t>40409818</t>
+  </si>
+  <si>
+    <t>01539176</t>
+  </si>
+  <si>
+    <t>04964843</t>
+  </si>
+  <si>
+    <t>40362968</t>
+  </si>
+  <si>
+    <t>09912844</t>
+  </si>
+  <si>
+    <t>43952255</t>
+  </si>
+  <si>
+    <t>02044816</t>
+  </si>
+  <si>
+    <t>20068854</t>
+  </si>
+  <si>
+    <t>24687727</t>
+  </si>
+  <si>
+    <t>20021387</t>
+  </si>
+  <si>
+    <t>42177491</t>
+  </si>
+  <si>
+    <t>80199159</t>
+  </si>
+  <si>
+    <t>02415430</t>
+  </si>
+  <si>
+    <t>43548231</t>
+  </si>
+  <si>
+    <t>23274872</t>
+  </si>
+  <si>
+    <t>45327547</t>
+  </si>
+  <si>
+    <t>28312018</t>
+  </si>
+  <si>
+    <t>75102983</t>
+  </si>
+  <si>
+    <t>80064592</t>
+  </si>
+  <si>
+    <t>44373731</t>
+  </si>
+  <si>
+    <t>47590083</t>
+  </si>
+  <si>
+    <t>41648714</t>
+  </si>
+  <si>
+    <t>01298035</t>
+  </si>
+  <si>
+    <t>45458628</t>
+  </si>
+  <si>
+    <t>40329505</t>
+  </si>
+  <si>
+    <t>42662941</t>
+  </si>
+  <si>
+    <t>44235236</t>
+  </si>
+  <si>
+    <t>72019595</t>
+  </si>
+  <si>
+    <t>80495492</t>
+  </si>
+  <si>
+    <t>43214084</t>
+  </si>
+  <si>
+    <t>41490357</t>
+  </si>
+  <si>
+    <t>41968733</t>
+  </si>
+  <si>
+    <t>47979613</t>
+  </si>
+  <si>
+    <t>80317947</t>
+  </si>
+  <si>
+    <t>42997341</t>
+  </si>
+  <si>
+    <t>43402622</t>
+  </si>
+  <si>
+    <t>42966692</t>
+  </si>
+  <si>
+    <t>02542365</t>
+  </si>
+  <si>
+    <t>44275274</t>
+  </si>
+  <si>
+    <t>45089074</t>
+  </si>
+  <si>
+    <t>28274549</t>
+  </si>
+  <si>
+    <t>41672593</t>
+  </si>
+  <si>
+    <t>42725445</t>
+  </si>
+  <si>
+    <t>24698674</t>
+  </si>
+  <si>
+    <t>42209895</t>
+  </si>
+  <si>
+    <t>73598701</t>
+  </si>
+  <si>
+    <t>28275688</t>
+  </si>
+  <si>
+    <t>80533325</t>
+  </si>
+  <si>
+    <t>47800527</t>
+  </si>
+  <si>
+    <t>47399870</t>
+  </si>
+  <si>
+    <t>42431271</t>
+  </si>
+  <si>
+    <t>40434746</t>
+  </si>
+  <si>
+    <t>46513926</t>
+  </si>
+  <si>
+    <t>08769965</t>
+  </si>
+  <si>
+    <t>45462179</t>
+  </si>
+  <si>
+    <t>44500977</t>
+  </si>
+  <si>
+    <t>44352393</t>
+  </si>
+  <si>
+    <t>40947821</t>
+  </si>
+  <si>
+    <t>09244927</t>
+  </si>
+  <si>
+    <t>47595131</t>
+  </si>
+  <si>
+    <t>71019123</t>
+  </si>
+  <si>
+    <t>10727102</t>
+  </si>
+  <si>
+    <t>20121617</t>
+  </si>
+  <si>
+    <t>77334799</t>
+  </si>
+  <si>
+    <t>06808878</t>
+  </si>
+  <si>
+    <t>48619119</t>
+  </si>
+  <si>
+    <t>70013083</t>
+  </si>
+  <si>
+    <t>40891715</t>
+  </si>
+  <si>
+    <t>70417820</t>
+  </si>
+  <si>
+    <t>43973895</t>
+  </si>
+  <si>
+    <t>73415532</t>
+  </si>
+  <si>
+    <t>74574874</t>
+  </si>
+  <si>
+    <t>43032559</t>
+  </si>
+  <si>
+    <t>24716362</t>
+  </si>
+  <si>
+    <t>44241105</t>
+  </si>
+  <si>
+    <t>02553630</t>
+  </si>
+  <si>
+    <t>77695480</t>
+  </si>
+  <si>
+    <t>41997576</t>
+  </si>
+  <si>
+    <t>48491974</t>
+  </si>
+  <si>
+    <t>73651334</t>
+  </si>
+  <si>
+    <t>61195518</t>
+  </si>
+  <si>
+    <t>76834183</t>
+  </si>
+  <si>
+    <t>00676531</t>
+  </si>
+  <si>
+    <t>73819477</t>
+  </si>
+  <si>
+    <t>40662325</t>
+  </si>
+  <si>
+    <t>02400679</t>
+  </si>
+  <si>
+    <t>02546169</t>
+  </si>
+  <si>
+    <t>42246125</t>
+  </si>
+  <si>
+    <t>02425316</t>
+  </si>
+  <si>
+    <t>73304687</t>
+  </si>
+  <si>
+    <t>10070171</t>
+  </si>
+  <si>
+    <t>46408032</t>
+  </si>
+  <si>
+    <t>71932329</t>
+  </si>
+  <si>
+    <t>46219653</t>
+  </si>
+  <si>
+    <t>40040184</t>
+  </si>
+  <si>
+    <t>30766789</t>
+  </si>
+  <si>
+    <t>31662709</t>
+  </si>
+  <si>
+    <t>46596554</t>
+  </si>
+  <si>
+    <t>43769088</t>
+  </si>
+  <si>
+    <t>02550498</t>
+  </si>
+  <si>
+    <t>40324519</t>
+  </si>
+  <si>
+    <t>46361156</t>
+  </si>
+  <si>
+    <t>80548721</t>
+  </si>
+  <si>
+    <t>44880553</t>
+  </si>
+  <si>
+    <t>04651038</t>
+  </si>
+  <si>
+    <t>42036243</t>
+  </si>
+  <si>
+    <t>01325351</t>
+  </si>
+  <si>
+    <t>43700994</t>
+  </si>
+  <si>
+    <t>01332505</t>
+  </si>
+  <si>
+    <t>04743900</t>
+  </si>
+  <si>
+    <t>46912053</t>
+  </si>
+  <si>
+    <t>70768801</t>
+  </si>
+  <si>
+    <t>75972848</t>
+  </si>
+  <si>
+    <t>28281963</t>
+  </si>
+  <si>
+    <t>46766546</t>
+  </si>
+  <si>
+    <t>42535729</t>
+  </si>
+  <si>
+    <t>42656588</t>
+  </si>
+  <si>
+    <t>29725729</t>
+  </si>
+  <si>
+    <t>60176663</t>
+  </si>
+  <si>
+    <t>43428679</t>
+  </si>
+  <si>
+    <t>40203991</t>
+  </si>
+  <si>
+    <t>70231653</t>
+  </si>
+  <si>
+    <t>76729252</t>
+  </si>
+  <si>
+    <t>45653803</t>
+  </si>
+  <si>
+    <t>47873581</t>
+  </si>
+  <si>
+    <t>42810487</t>
+  </si>
+  <si>
+    <t>46152948</t>
+  </si>
+  <si>
+    <t>47604404</t>
+  </si>
+  <si>
+    <t>02527553</t>
+  </si>
+  <si>
+    <t>41586331</t>
+  </si>
+  <si>
+    <t>72251136</t>
+  </si>
+  <si>
+    <t>70355875</t>
+  </si>
+  <si>
+    <t>73547288</t>
+  </si>
+  <si>
+    <t>44978131</t>
+  </si>
+  <si>
+    <t>46532376</t>
+  </si>
+  <si>
+    <t>41981402</t>
+  </si>
+  <si>
+    <t>46265351</t>
+  </si>
+  <si>
+    <t>48149851</t>
+  </si>
+  <si>
+    <t>02545100</t>
+  </si>
+  <si>
+    <t>75021649</t>
+  </si>
+  <si>
+    <t>44704653</t>
+  </si>
+  <si>
+    <t>43920887</t>
+  </si>
+  <si>
+    <t>42492796</t>
+  </si>
+  <si>
+    <t>80113798</t>
+  </si>
+  <si>
+    <t>44959881</t>
+  </si>
+  <si>
+    <t>43562527</t>
+  </si>
+  <si>
+    <t>74497311</t>
+  </si>
+  <si>
+    <t>41793992</t>
+  </si>
+  <si>
+    <t>05958276</t>
+  </si>
+  <si>
+    <t>77500742</t>
+  </si>
+  <si>
+    <t>47037763</t>
+  </si>
+  <si>
+    <t>25218719</t>
+  </si>
+  <si>
+    <t>42972864</t>
+  </si>
+  <si>
+    <t>41445238</t>
+  </si>
+  <si>
+    <t>46014139</t>
+  </si>
+  <si>
+    <t>47656024</t>
+  </si>
+  <si>
+    <t>00444615</t>
+  </si>
+  <si>
+    <t>46331842</t>
+  </si>
+  <si>
+    <t>44164626</t>
+  </si>
+  <si>
+    <t>10576320</t>
+  </si>
+  <si>
+    <t>10036451</t>
+  </si>
+  <si>
+    <t>73593686</t>
+  </si>
+  <si>
+    <t>41138839</t>
+  </si>
+  <si>
+    <t>43922995</t>
+  </si>
+  <si>
+    <t>41297310</t>
+  </si>
+  <si>
+    <t>04640909</t>
+  </si>
+  <si>
+    <t>APAZA MAMANI ALFREDO ALBERTO</t>
+  </si>
+  <si>
+    <t>ASTUDILLO BERAUN LUIS ALBERTO</t>
+  </si>
+  <si>
+    <t>ATANACIO BERROSPI SOCIMO</t>
+  </si>
+  <si>
+    <t>BRITO PINTADO OSCAR ALFONSO</t>
+  </si>
+  <si>
+    <t>CACERES ROJAS GARY JOSE</t>
+  </si>
+  <si>
+    <t>CCALLOCONDO GUTIERREZ JAVIER</t>
+  </si>
+  <si>
+    <t>CHUQUIYAURI TEODORO ALFREDO</t>
+  </si>
+  <si>
+    <t>CORONADO JAVIER FLORENCIO</t>
+  </si>
+  <si>
+    <t>DAGA INOCENTE JOSE LUIS</t>
+  </si>
+  <si>
+    <t>ESTELA ORDOÑEZ WAGNER NEISSER</t>
+  </si>
+  <si>
+    <t>GRIJALVA BAJALQUE ARNOLD JUNIOR</t>
+  </si>
+  <si>
+    <t>LEDEZMA PIHUE JORGE LUIS</t>
+  </si>
+  <si>
+    <t>MAMANI HUAHUALUQUE PRIMO FELICIANO</t>
+  </si>
+  <si>
+    <t>MAMANI MAMANI EULER</t>
+  </si>
+  <si>
+    <t>QUISPE CONDORI ARMANDO</t>
+  </si>
+  <si>
+    <t>QUISPE QUEA LUCIO ELMER</t>
+  </si>
+  <si>
+    <t>QUISPE TICONA HECTOR RUBEN</t>
+  </si>
+  <si>
+    <t>RAMOS CALLA WILLIAM</t>
+  </si>
+  <si>
+    <t>ROQUE GUERRERO RAFAEL ROMEL</t>
+  </si>
+  <si>
+    <t>TESEN MAYANGA JAIME</t>
+  </si>
+  <si>
+    <t>TRONCOSO AMPA ALI JOSUE</t>
+  </si>
+  <si>
+    <t>TURPO ORTIZ PAUL VICENTE</t>
+  </si>
+  <si>
+    <t>UTURUNCO ORTIZ VALERIO</t>
+  </si>
+  <si>
+    <t>ZAPATA CHAMBI RONALD JULIO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA RETAMOZO YANITZE VANIA</t>
   </si>
 </sst>
 </file>
@@ -1618,7 +1747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD330490-A8A1-49E3-86FF-A6622C7A89BB}">
-  <dimension ref="A1:B222"/>
+  <dimension ref="A1:B244"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="1"/>
@@ -1635,7 +1764,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -1643,7 +1772,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -1651,7 +1780,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -1659,15 +1788,15 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>373</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -1675,7 +1804,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>6</v>
@@ -1683,7 +1812,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
@@ -1691,1714 +1820,1890 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>8</v>
+        <v>422</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="1">
-        <v>65026173</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="1" t="s">
-        <v>202</v>
+      <c r="A13" s="1">
+        <v>40752658</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>11</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>14</v>
+        <v>423</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>15</v>
+        <v>424</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>374</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="1">
-        <v>65017248</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="1">
-        <v>65040221</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>151</v>
+        <v>425</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>152</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="1" t="s">
-        <v>213</v>
+      <c r="A26" s="1">
+        <v>70295470</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>21</v>
+        <v>426</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>216</v>
+        <v>245</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>22</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>375</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>218</v>
+        <v>247</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>219</v>
+        <v>248</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>376</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="1">
-        <v>65005966</v>
+      <c r="A34" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>377</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>24</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="1">
-        <v>65013041</v>
+      <c r="A37" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>156</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="1" t="s">
-        <v>223</v>
+      <c r="A38" s="1">
+        <v>10814161</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>25</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="1">
-        <v>65046612</v>
+      <c r="A39" s="1" t="s">
+        <v>254</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>26</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>378</v>
+        <v>427</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="1" t="s">
-        <v>226</v>
+      <c r="A42" s="1">
+        <v>24006626</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>28</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>142</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="1" t="s">
-        <v>228</v>
+      <c r="A44" s="1">
+        <v>71831646</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>379</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>229</v>
+        <v>258</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>29</v>
+        <v>194</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="1" t="s">
-        <v>230</v>
+      <c r="A46" s="1">
+        <v>29547818</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="1">
-        <v>65046842</v>
+      <c r="A47" s="1" t="s">
+        <v>259</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>31</v>
+        <v>195</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>143</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="1" t="s">
-        <v>234</v>
+      <c r="A51" s="1">
+        <v>46218602</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="1">
-        <v>65046841</v>
+      <c r="A52" s="1" t="s">
+        <v>263</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>159</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>33</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>34</v>
+        <v>428</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>380</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>35</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>36</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="1">
-        <v>65027981</v>
+      <c r="A58" s="1" t="s">
+        <v>269</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>381</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>38</v>
+        <v>196</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>39</v>
+        <v>429</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>382</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>41</v>
+        <v>197</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>160</v>
+        <v>37</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>383</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>43</v>
+        <v>430</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>384</v>
+        <v>39</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>44</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>186</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>385</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>45</v>
+        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>46</v>
+        <v>431</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>47</v>
+        <v>199</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>49</v>
+        <v>200</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="1" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>51</v>
+        <v>184</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="1" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>161</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="1">
-        <v>65038312</v>
+      <c r="A83" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>386</v>
+        <v>432</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="1">
-        <v>65001245</v>
+      <c r="A84" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="1" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="1" t="s">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="1" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="1" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>144</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="1" t="s">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="1" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="1">
-        <v>65045969</v>
+      <c r="A91" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>387</v>
+        <v>160</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="1" t="s">
-        <v>270</v>
+      <c r="A92" s="1">
+        <v>48422313</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>58</v>
+        <v>202</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="1" t="s">
-        <v>271</v>
+      <c r="A93" s="1">
+        <v>31677451</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>388</v>
+        <v>52</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="1" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>389</v>
+        <v>53</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="1" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="1">
-        <v>65000629</v>
+      <c r="A96" s="1" t="s">
+        <v>305</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="1" t="s">
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="1" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="1" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="1" t="s">
-        <v>277</v>
+      <c r="A100" s="1">
+        <v>70269493</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>64</v>
+        <v>203</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="1">
-        <v>65043806</v>
+      <c r="A101" s="1" t="s">
+        <v>309</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="1" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>66</v>
+        <v>204</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>390</v>
+        <v>205</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="1" t="s">
-        <v>281</v>
+      <c r="A105" s="1">
+        <v>42305005</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="1" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="1">
-        <v>65046315</v>
+      <c r="A107" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="1" t="s">
-        <v>283</v>
+        <v>315</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="1" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="1" t="s">
-        <v>285</v>
+      <c r="A110" s="1">
+        <v>46881401</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="1" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="1" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>74</v>
+        <v>433</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>75</v>
+        <v>206</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="1">
-        <v>65010243</v>
+      <c r="A114" s="1" t="s">
+        <v>320</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="1" t="s">
-        <v>289</v>
+      <c r="A115" s="1">
+        <v>41996873</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="1">
-        <v>65044422</v>
+      <c r="A116" s="1" t="s">
+        <v>321</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="1" t="s">
-        <v>290</v>
+      <c r="A117" s="1">
+        <v>32882008</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="1" t="s">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="1" t="s">
-        <v>292</v>
+        <v>323</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="1" t="s">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="1" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>164</v>
+        <v>72</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="1" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="1" t="s">
-        <v>296</v>
+        <v>327</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>146</v>
+        <v>74</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="1" t="s">
-        <v>297</v>
+      <c r="A124" s="1">
+        <v>20427241</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="1" t="s">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>165</v>
+        <v>76</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="1" t="s">
-        <v>299</v>
+      <c r="A126" s="1">
+        <v>46217452</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="1" t="s">
-        <v>300</v>
+        <v>329</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="1" t="s">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>391</v>
+        <v>78</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="1" t="s">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="1" t="s">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>85</v>
+        <v>434</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="1" t="s">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="1" t="s">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>87</v>
+        <v>435</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="1" t="s">
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="1" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="1">
-        <v>65046129</v>
+      <c r="A135" s="1" t="s">
+        <v>337</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="1" t="s">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="1" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="1" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="1" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>90</v>
+        <v>165</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="1">
-        <v>65014143</v>
+      <c r="A140" s="1" t="s">
+        <v>342</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="1" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="1" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="1" t="s">
-        <v>314</v>
+        <v>345</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>148</v>
+        <v>85</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="1" t="s">
-        <v>315</v>
+        <v>346</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="1">
-        <v>65039713</v>
+      <c r="A145" s="1" t="s">
+        <v>347</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>392</v>
+        <v>186</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="1" t="s">
-        <v>316</v>
+        <v>348</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>93</v>
+        <v>146</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="1" t="s">
-        <v>317</v>
+      <c r="A147" s="1">
+        <v>10091490</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>94</v>
+        <v>167</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="1">
-        <v>65039692</v>
+      <c r="A148" s="1" t="s">
+        <v>349</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="1" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>393</v>
+        <v>168</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="1">
-        <v>65046254</v>
+      <c r="A150" s="1" t="s">
+        <v>351</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>172</v>
+        <v>88</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="1" t="s">
-        <v>319</v>
+        <v>352</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>173</v>
+        <v>89</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="1" t="s">
-        <v>320</v>
+      <c r="A152" s="1">
+        <v>26706595</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>96</v>
+        <v>169</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="1">
-        <v>65046869</v>
+      <c r="A153" s="1" t="s">
+        <v>353</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="1" t="s">
-        <v>321</v>
+        <v>354</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="1" t="s">
-        <v>322</v>
+        <v>355</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>98</v>
+        <v>147</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="1" t="s">
-        <v>323</v>
+        <v>356</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="1" t="s">
-        <v>324</v>
+      <c r="A157" s="1">
+        <v>45505096</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>100</v>
+        <v>208</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="1" t="s">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="1" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="1" t="s">
-        <v>327</v>
+      <c r="A160" s="1">
+        <v>60820639</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="1" t="s">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>104</v>
+        <v>209</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="1" t="s">
-        <v>329</v>
+      <c r="A162" s="1">
+        <v>76239928</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>105</v>
+        <v>171</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="1">
-        <v>65022074</v>
+      <c r="A163" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>106</v>
+        <v>172</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="1">
-        <v>65000059</v>
+      <c r="A164" s="1" t="s">
+        <v>361</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>175</v>
+        <v>95</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="1" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>107</v>
+        <v>173</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="1" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="1" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>176</v>
+        <v>97</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="1">
-        <v>65046892</v>
+      <c r="A168" s="1" t="s">
+        <v>365</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>394</v>
+        <v>98</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="1">
-        <v>65046889</v>
+      <c r="A169" s="1" t="s">
+        <v>366</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>395</v>
+        <v>99</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="1" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="1">
-        <v>65040852</v>
+      <c r="A171" s="1" t="s">
+        <v>368</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>177</v>
+        <v>101</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="1" t="s">
-        <v>334</v>
+        <v>369</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="1" t="s">
-        <v>335</v>
+        <v>370</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>396</v>
+        <v>103</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="1" t="s">
-        <v>336</v>
+        <v>371</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>397</v>
+        <v>104</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="1" t="s">
-        <v>337</v>
+      <c r="A175" s="1">
+        <v>43539336</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>178</v>
+        <v>105</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="1" t="s">
-        <v>338</v>
+      <c r="A176" s="1">
+        <v>10874713</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="1" t="s">
-        <v>339</v>
+        <v>372</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="1" t="s">
-        <v>340</v>
+        <v>373</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="1" t="s">
-        <v>341</v>
+        <v>374</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>113</v>
+        <v>175</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="1">
-        <v>65029567</v>
+        <v>46318470</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>114</v>
+        <v>210</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="1" t="s">
-        <v>342</v>
+        <v>375</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>115</v>
+        <v>436</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="1" t="s">
-        <v>343</v>
+      <c r="A182" s="1">
+        <v>71305125</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>149</v>
+        <v>211</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="1" t="s">
-        <v>344</v>
+        <v>376</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="1" t="s">
-        <v>345</v>
+      <c r="A184" s="1">
+        <v>28597752</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="1" t="s">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>398</v>
+        <v>437</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="1" t="s">
-        <v>347</v>
+        <v>378</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>189</v>
+        <v>438</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="1">
-        <v>65004432</v>
+        <v>31601357</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>180</v>
+        <v>109</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="1">
-        <v>65008689</v>
+      <c r="A188" s="1" t="s">
+        <v>379</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>181</v>
+        <v>439</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="1">
-        <v>65009305</v>
+      <c r="A189" s="1" t="s">
+        <v>380</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>118</v>
+        <v>212</v>
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="1">
-        <v>65045074</v>
+      <c r="A190" s="1" t="s">
+        <v>381</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>119</v>
+        <v>213</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="1" t="s">
-        <v>348</v>
+      <c r="A191" s="1">
+        <v>70206733</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>120</v>
+        <v>177</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="1" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>121</v>
+        <v>178</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="1" t="s">
-        <v>350</v>
+        <v>383</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="1">
-        <v>65001613</v>
+      <c r="A194" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" s="1" t="s">
-        <v>351</v>
+        <v>385</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="1" t="s">
-        <v>352</v>
+      <c r="A196" s="1">
+        <v>40052591</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>190</v>
+        <v>113</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" s="1" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" s="1" t="s">
-        <v>354</v>
+        <v>387</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="1">
-        <v>65027410</v>
+      <c r="A199" s="1" t="s">
+        <v>388</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" s="1" t="s">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>182</v>
+        <v>116</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" s="1" t="s">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>128</v>
+        <v>440</v>
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="1" t="s">
-        <v>357</v>
+      <c r="A202" s="1">
+        <v>7093320</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" s="1" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>129</v>
+        <v>187</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" s="1">
-        <v>65044717</v>
+        <v>40105597</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>399</v>
+        <v>179</v>
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="1" t="s">
-        <v>359</v>
+      <c r="A205" s="1">
+        <v>20659538</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>130</v>
+        <v>180</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" s="1">
-        <v>65015143</v>
+        <v>40782264</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>400</v>
+        <v>117</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="1" t="s">
-        <v>360</v>
+      <c r="A207" s="1">
+        <v>76465704</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
     </row>
     <row r="208" spans="1:2">
-      <c r="A208" s="1">
-        <v>65046264</v>
+      <c r="A208" s="1" t="s">
+        <v>392</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>183</v>
+        <v>119</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" s="1" t="s">
-        <v>361</v>
+        <v>393</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" s="1" t="s">
-        <v>362</v>
+        <v>394</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>401</v>
+        <v>121</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="1" t="s">
-        <v>363</v>
+      <c r="A211" s="1">
+        <v>10663914</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" s="1" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" s="1" t="s">
-        <v>365</v>
+        <v>396</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" s="1" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>135</v>
+        <v>441</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" s="1" t="s">
-        <v>367</v>
+        <v>398</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>185</v>
+        <v>124</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="1">
-        <v>65041388</v>
+      <c r="A216" s="1" t="s">
+        <v>399</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="1" t="s">
-        <v>368</v>
+      <c r="A217" s="1">
+        <v>42198740</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" s="1" t="s">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>402</v>
+        <v>181</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219" s="1" t="s">
-        <v>370</v>
+        <v>401</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>137</v>
+        <v>442</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="1">
-        <v>65046940</v>
+      <c r="A221" s="1" t="s">
+        <v>403</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>403</v>
+        <v>189</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" s="1" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="1">
+        <v>71741888</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="1">
+        <v>44202404</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="1">
+        <v>72637021</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="1">
+        <v>43928099</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="1">
+        <v>48434434</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>446</v>
       </c>
     </row>
   </sheetData>

--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sbuendia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B546CD24-87F6-4B4B-A7E0-3BD09A5ADA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E973530-46AF-46D3-9926-4D0BE82B7B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{878F31C5-4CEA-4304-87C5-39FC92D222CB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="523">
   <si>
     <t>DNI</t>
   </si>
@@ -84,9 +84,6 @@
     <t>AUCCAPIÑA QUISPE EUSEBIO</t>
   </si>
   <si>
-    <t>AYMA MAYTA YUDE</t>
-  </si>
-  <si>
     <t>BALBIN RAMOS CESAR ALBERTO</t>
   </si>
   <si>
@@ -348,9 +345,6 @@
     <t>PINEDO VARGAS ELVIS</t>
   </si>
   <si>
-    <t>POMAHUACRE PRADO NELSON</t>
-  </si>
-  <si>
     <t>PONCE DE LEON LEONARDO LUIS MIGUEL</t>
   </si>
   <si>
@@ -534,9 +528,6 @@
     <t>MARIN FIGUEROA JUAN BAUTISTA</t>
   </si>
   <si>
-    <t>MASIAS SALDIVAR AMILCAR</t>
-  </si>
-  <si>
     <t>MILLAN QUINTANILLA JHOEL</t>
   </si>
   <si>
@@ -549,9 +540,6 @@
     <t>MUÑOZ VILLACORTA ROMARIO</t>
   </si>
   <si>
-    <t>PALOMINO DELGADILLO ESTEFANY HEYDI</t>
-  </si>
-  <si>
     <t>PANOCA ALANIA RUYER EDGARDO</t>
   </si>
   <si>
@@ -606,9 +594,6 @@
     <t>TTITO JUSTINIANI HECTOR</t>
   </si>
   <si>
-    <t>CAPANI MATAMOROS WALTER</t>
-  </si>
-  <si>
     <t>CARHUANCHO PEREZ RAUL RENATO</t>
   </si>
   <si>
@@ -654,18 +639,12 @@
     <t>MASCO GOMEZ GERARDO DIONICIO</t>
   </si>
   <si>
-    <t>OLOYA JUAREZ MILTON DANILO</t>
-  </si>
-  <si>
     <t>PAITAN QUISPE SIMEON</t>
   </si>
   <si>
     <t>QUISPE CHURA ROGELIO</t>
   </si>
   <si>
-    <t>QUISPE GARCIA LEONARD</t>
-  </si>
-  <si>
     <t>RAMOS CANCHO JOSEIN WILDER</t>
   </si>
   <si>
@@ -684,18 +663,12 @@
     <t>VASQUEZ CARRASCO JENNSON</t>
   </si>
   <si>
-    <t>YPANAQUE AMAYA EDIN</t>
-  </si>
-  <si>
     <t>ZAPANA TURPO SUSY </t>
   </si>
   <si>
     <t>09874967</t>
   </si>
   <si>
-    <t>00409316</t>
-  </si>
-  <si>
     <t>10604841</t>
   </si>
   <si>
@@ -729,18 +702,12 @@
     <t>40844695</t>
   </si>
   <si>
-    <t>48243054</t>
-  </si>
-  <si>
     <t>43728469</t>
   </si>
   <si>
     <t>24494456</t>
   </si>
   <si>
-    <t>41004089</t>
-  </si>
-  <si>
     <t>40303753</t>
   </si>
   <si>
@@ -777,9 +744,6 @@
     <t>40974286</t>
   </si>
   <si>
-    <t>44499928</t>
-  </si>
-  <si>
     <t>43354084</t>
   </si>
   <si>
@@ -1050,9 +1014,6 @@
     <t>02546169</t>
   </si>
   <si>
-    <t>42246125</t>
-  </si>
-  <si>
     <t>02425316</t>
   </si>
   <si>
@@ -1134,9 +1095,6 @@
     <t>46766546</t>
   </si>
   <si>
-    <t>42535729</t>
-  </si>
-  <si>
     <t>42656588</t>
   </si>
   <si>
@@ -1191,9 +1149,6 @@
     <t>44978131</t>
   </si>
   <si>
-    <t>46532376</t>
-  </si>
-  <si>
     <t>41981402</t>
   </si>
   <si>
@@ -1269,9 +1224,6 @@
     <t>10576320</t>
   </si>
   <si>
-    <t>10036451</t>
-  </si>
-  <si>
     <t>73593686</t>
   </si>
   <si>
@@ -1338,9 +1290,6 @@
     <t>RAMOS CALLA WILLIAM</t>
   </si>
   <si>
-    <t>ROQUE GUERRERO RAFAEL ROMEL</t>
-  </si>
-  <si>
     <t>TESEN MAYANGA JAIME</t>
   </si>
   <si>
@@ -1365,12 +1314,6 @@
     <t>02709902</t>
   </si>
   <si>
-    <t>04339015</t>
-  </si>
-  <si>
-    <t>77472844</t>
-  </si>
-  <si>
     <t>76517298</t>
   </si>
   <si>
@@ -1407,9 +1350,6 @@
     <t>80283617</t>
   </si>
   <si>
-    <t>79148978</t>
-  </si>
-  <si>
     <t>44925309</t>
   </si>
   <si>
@@ -1452,12 +1392,6 @@
     <t>APONTE CARRASCO MANUEL EUGENIO</t>
   </si>
   <si>
-    <t>CABRERA AGUILAR EMERSON JOHN</t>
-  </si>
-  <si>
-    <t>CALVA GARCIA HEBERT MIGUEL</t>
-  </si>
-  <si>
     <t>CCASO CONDORI BERTHA</t>
   </si>
   <si>
@@ -1503,12 +1437,6 @@
     <t>MACEDO ESQUIA MAURO</t>
   </si>
   <si>
-    <t>MACHADO CHIROQUE PEDRO ELIAS</t>
-  </si>
-  <si>
-    <t>MARTINEZ OYARCE ERNESTO</t>
-  </si>
-  <si>
     <t>PINTO LUQUE ROSA EUSEBIA</t>
   </si>
   <si>
@@ -1552,6 +1480,132 @@
   </si>
   <si>
     <t>ZEVALLOS CHIRA JHIMI YURIN</t>
+  </si>
+  <si>
+    <t>70345043</t>
+  </si>
+  <si>
+    <t>41140870</t>
+  </si>
+  <si>
+    <t>10430145</t>
+  </si>
+  <si>
+    <t>40019423</t>
+  </si>
+  <si>
+    <t>76507703</t>
+  </si>
+  <si>
+    <t>09858360</t>
+  </si>
+  <si>
+    <t>46070283</t>
+  </si>
+  <si>
+    <t>48464641</t>
+  </si>
+  <si>
+    <t>48044236</t>
+  </si>
+  <si>
+    <t>47671392</t>
+  </si>
+  <si>
+    <t>80510756</t>
+  </si>
+  <si>
+    <t>20106471</t>
+  </si>
+  <si>
+    <t>42025506</t>
+  </si>
+  <si>
+    <t>70167449</t>
+  </si>
+  <si>
+    <t>02415507</t>
+  </si>
+  <si>
+    <t>44515489</t>
+  </si>
+  <si>
+    <t>03870152</t>
+  </si>
+  <si>
+    <t>09613354</t>
+  </si>
+  <si>
+    <t>41761006</t>
+  </si>
+  <si>
+    <t>APONTE CHINGA RICHARD RONALDO</t>
+  </si>
+  <si>
+    <t>ARANA MAMANI GUILLERMO</t>
+  </si>
+  <si>
+    <t>BALDEON NUÑEZ JEOVANI GREGORIO</t>
+  </si>
+  <si>
+    <t>CAMPOS DELGADO EVER TEODOMIRO</t>
+  </si>
+  <si>
+    <t>CASTILLO INGA JUSTO DAVID</t>
+  </si>
+  <si>
+    <t>DAVILA ROJAS ORLANDO</t>
+  </si>
+  <si>
+    <t>DURAND BARRIENTOS MARIO</t>
+  </si>
+  <si>
+    <t>GAVIDIA HINOJOSA DANIEL FERNANDO</t>
+  </si>
+  <si>
+    <t>INOCENTE MANRIQUE NESTOR JULIO</t>
+  </si>
+  <si>
+    <t>LOPA CHANCO BRAULIO</t>
+  </si>
+  <si>
+    <t>LOPEZ PIZAN FREDY CARLOS</t>
+  </si>
+  <si>
+    <t>LOPEZ SALAZAR MONICA BERTHA</t>
+  </si>
+  <si>
+    <t>MAU FARFAN CARLOS VICENTE</t>
+  </si>
+  <si>
+    <t>MEDINA BERROCAL BASILIO</t>
+  </si>
+  <si>
+    <t>MESIAS ROBATTI MARCOS YURI</t>
+  </si>
+  <si>
+    <t>MIRANDA SANCHEZ LUIS MIGUEL</t>
+  </si>
+  <si>
+    <t>QUEQUEJANA CONDORI MIGUEL ELISEO</t>
+  </si>
+  <si>
+    <t>TARQUI TACORA ISMAEL</t>
+  </si>
+  <si>
+    <t>VARGAS TORRES JOSE WALDIR</t>
+  </si>
+  <si>
+    <t>VEGA CHACALIAZA CARLOS JAVIER</t>
+  </si>
+  <si>
+    <t>VILCHEZ TORRES VICTOR JULIO</t>
+  </si>
+  <si>
+    <t>VILLALOBOS TRUJILLANO TORIBIO</t>
+  </si>
+  <si>
+    <t>YALLICO LLACTAHUAMAN YURI</t>
   </si>
 </sst>
 </file>
@@ -1927,7 +1981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD330490-A8A1-49E3-86FF-A6622C7A89BB}">
-  <dimension ref="A1:B276"/>
+  <dimension ref="A1:B286"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.21875" style="1"/>
@@ -1944,15 +1998,15 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>218</v>
+      <c r="A3" s="1">
+        <v>409316</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -1960,7 +2014,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -1968,15 +2022,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>469</v>
+        <v>449</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -1984,7 +2038,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>6</v>
@@ -1992,7 +2046,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
@@ -2000,15 +2054,15 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>8</v>
@@ -2016,242 +2070,242 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>225</v>
+        <v>481</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>9</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>40752658</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>227</v>
+        <v>482</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>11</v>
+        <v>501</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>228</v>
+      <c r="A16" s="1">
+        <v>40752658</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>12</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>417</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>418</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>13</v>
+        <v>401</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>232</v>
+      <c r="A20" s="1">
+        <v>48243054</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>14</v>
+        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>236</v>
+        <v>483</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>18</v>
+        <v>502</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>70295470</v>
+      <c r="A27" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>139</v>
+        <v>403</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>149</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>442</v>
+      <c r="A29" s="1">
+        <v>70295470</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>471</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>420</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>150</v>
+        <v>404</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>151</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>443</v>
+        <v>234</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>472</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>246</v>
+        <v>484</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>189</v>
+        <v>503</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -2259,1887 +2313,1967 @@
         <v>10814161</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>251</v>
+        <v>485</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>421</v>
+        <v>504</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>24</v>
+        <v>405</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>444</v>
+        <v>240</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>473</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
+      <c r="A46" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
         <v>24006626</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="B47" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>43232825</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>71831646</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
-        <v>43232825</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
-        <v>71831646</v>
-      </c>
-      <c r="B50" s="2" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>29547818</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
-        <v>29547818</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>193</v>
+        <v>138</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>446</v>
+        <v>245</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>476</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>258</v>
+        <v>427</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>29</v>
+        <v>454</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
+      <c r="A58" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
         <v>46218602</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="B59" s="2" t="s">
-        <v>30</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>141</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>447</v>
+        <v>248</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>477</v>
+        <v>139</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>261</v>
+        <v>428</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>422</v>
+        <v>455</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>31</v>
+        <v>406</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>448</v>
+        <v>250</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>478</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>263</v>
+        <v>429</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>156</v>
+        <v>456</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>32</v>
+        <v>155</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>423</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>34</v>
+        <v>407</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>449</v>
+        <v>257</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>479</v>
+        <v>34</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>270</v>
+        <v>430</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>194</v>
+        <v>457</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>36</v>
+        <v>189</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>424</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>39</v>
+        <v>408</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>195</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="1" t="s">
-        <v>277</v>
+      <c r="A80" s="1">
+        <v>42064755</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>40</v>
+        <v>505</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>41</v>
+        <v>190</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>158</v>
+        <v>39</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>280</v>
+        <v>486</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>425</v>
+        <v>506</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>196</v>
+        <v>40</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>42</v>
+        <v>156</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>197</v>
+        <v>409</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>43</v>
+        <v>191</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>450</v>
+        <v>270</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>480</v>
+        <v>41</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>198</v>
+        <v>42</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>44</v>
+        <v>458</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>45</v>
+        <v>179</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>426</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94" s="1" t="s">
-        <v>451</v>
+      <c r="A94" s="1">
+        <v>24464607</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>481</v>
+        <v>507</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>48</v>
+        <v>410</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>293</v>
+        <v>432</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>49</v>
+        <v>459</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>184</v>
+        <v>46</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101" s="1">
-        <v>72746477</v>
+      <c r="A101" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>482</v>
+        <v>47</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>159</v>
+        <v>49</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A104" s="1">
-        <v>48422313</v>
+      <c r="A104" s="1" t="s">
+        <v>283</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
-        <v>31677451</v>
+        <v>72746477</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>52</v>
+        <v>460</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>452</v>
+        <v>285</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>483</v>
+        <v>157</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A108" s="1" t="s">
-        <v>299</v>
+      <c r="A108" s="1">
+        <v>48422313</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>54</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A109" s="1" t="s">
-        <v>300</v>
+      <c r="A109" s="1">
+        <v>31677451</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>142</v>
+        <v>52</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>302</v>
+        <v>433</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>143</v>
+        <v>461</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A113" s="1">
-        <v>70269493</v>
+      <c r="A113" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>200</v>
+        <v>54</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>201</v>
+        <v>141</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>453</v>
+        <v>291</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>484</v>
+        <v>55</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A117" s="1" t="s">
-        <v>306</v>
+      <c r="A117" s="1">
+        <v>70269493</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A119" s="1">
-        <v>42305005</v>
+      <c r="A119" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>59</v>
+        <v>196</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>308</v>
+        <v>434</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>60</v>
+        <v>462</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>61</v>
+        <v>197</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A123" s="1" t="s">
-        <v>311</v>
+      <c r="A123" s="1">
+        <v>42305005</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>312</v>
+        <v>487</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>64</v>
+        <v>508</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>454</v>
+        <v>296</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>485</v>
+        <v>59</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>203</v>
+        <v>60</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A128" s="1">
-        <v>41996873</v>
+      <c r="A128" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A130" s="1">
-        <v>32882008</v>
+      <c r="A130" s="1" t="s">
+        <v>435</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>160</v>
+        <v>463</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>68</v>
+        <v>198</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A133" s="1" t="s">
-        <v>318</v>
+      <c r="A133" s="1">
+        <v>41996873</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A135" s="1" t="s">
-        <v>320</v>
+      <c r="A135" s="1">
+        <v>32882008</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A137" s="1">
-        <v>20427241</v>
+      <c r="A137" s="1" t="s">
+        <v>305</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A138" s="1">
-        <v>43004567</v>
+      <c r="A138" s="1" t="s">
+        <v>306</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>486</v>
+        <v>69</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>322</v>
+        <v>488</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>75</v>
+        <v>509</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A140" s="1">
-        <v>46217452</v>
+      <c r="A140" s="1" t="s">
+        <v>307</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>487</v>
+        <v>510</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>456</v>
+        <v>308</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>488</v>
+        <v>71</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>323</v>
+        <v>490</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>161</v>
+        <v>511</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A145" s="1" t="s">
-        <v>325</v>
+      <c r="A145" s="1">
+        <v>20427241</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A146" s="1" t="s">
-        <v>326</v>
+      <c r="A146" s="1">
+        <v>43004567</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>427</v>
+        <v>464</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A148" s="1" t="s">
-        <v>328</v>
+      <c r="A148" s="1">
+        <v>46217452</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>428</v>
+        <v>75</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>329</v>
+        <v>436</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>162</v>
+        <v>465</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>80</v>
+        <v>159</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>144</v>
+        <v>76</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>163</v>
+        <v>411</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>164</v>
+        <v>412</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A156" s="1">
-        <v>42394596</v>
+      <c r="A156" s="1" t="s">
+        <v>317</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>489</v>
+        <v>160</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>204</v>
+        <v>79</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>84</v>
+        <v>161</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A164" s="1">
-        <v>10091490</v>
+      <c r="A164" s="1" t="s">
+        <v>491</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>166</v>
+        <v>512</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>167</v>
+        <v>83</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>345</v>
+        <v>492</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>87</v>
+        <v>513</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A169" s="1">
-        <v>26706595</v>
+      <c r="A169" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>347</v>
+        <v>493</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>169</v>
+        <v>514</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A172" s="1" t="s">
-        <v>349</v>
+      <c r="A172" s="1">
+        <v>10091490</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A174" s="1">
-        <v>45505096</v>
+      <c r="A174" s="1" t="s">
+        <v>494</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>205</v>
+        <v>515</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>91</v>
+        <v>164</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A177" s="1">
-        <v>60820639</v>
+      <c r="A177" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A178" s="1" t="s">
-        <v>353</v>
+      <c r="A178" s="1">
+        <v>26706595</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>206</v>
+        <v>165</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A179" s="1">
-        <v>76239928</v>
+      <c r="A179" s="1" t="s">
+        <v>334</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>171</v>
+        <v>88</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>172</v>
+        <v>89</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A185" s="1" t="s">
-        <v>359</v>
+      <c r="A185" s="1">
+        <v>60820639</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>98</v>
+        <v>200</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
-        <v>457</v>
+        <v>345</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>490</v>
+        <v>95</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A193" s="1">
-        <v>43539336</v>
+      <c r="A193" s="1" t="s">
+        <v>347</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A194" s="1">
-        <v>10874713</v>
+      <c r="A194" s="1" t="s">
+        <v>348</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>173</v>
+        <v>98</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>174</v>
+        <v>101</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A198" s="1">
-        <v>46318470</v>
+      <c r="A198" s="1" t="s">
+        <v>437</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>207</v>
+        <v>466</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A199" s="1" t="s">
-        <v>369</v>
+      <c r="A199" s="1">
+        <v>43539336</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>429</v>
+        <v>102</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
-        <v>71305125</v>
+        <v>10874713</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A202" s="1">
-        <v>28597752</v>
+      <c r="A202" s="1" t="s">
+        <v>353</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>175</v>
+        <v>104</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
-        <v>458</v>
+        <v>495</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>491</v>
+        <v>516</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>430</v>
+        <v>170</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A205" s="1" t="s">
-        <v>372</v>
+      <c r="A205" s="1">
+        <v>46318470</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>431</v>
+        <v>201</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>459</v>
+        <v>355</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>492</v>
+        <v>413</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A207" s="1">
-        <v>31601357</v>
+      <c r="A207" s="1" t="s">
+        <v>356</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A208" s="1" t="s">
-        <v>373</v>
+      <c r="A208" s="1">
+        <v>28597752</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>432</v>
+        <v>171</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
-        <v>374</v>
+        <v>438</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>209</v>
+        <v>467</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>210</v>
+        <v>414</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A211" s="1">
-        <v>70206733</v>
+      <c r="A211" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>176</v>
+        <v>415</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>376</v>
+        <v>439</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>177</v>
+        <v>468</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A213" s="1" t="s">
-        <v>377</v>
+      <c r="A213" s="1">
+        <v>31601357</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>110</v>
+        <v>416</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A215" s="1">
-        <v>32130322</v>
+      <c r="A215" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>493</v>
+        <v>202</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
-        <v>40052591</v>
+        <v>70206733</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
-        <v>460</v>
+        <v>363</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>494</v>
+        <v>107</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
-        <v>41929747</v>
+        <v>32130322</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>495</v>
+        <v>469</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A223" s="1" t="s">
-        <v>383</v>
+      <c r="A223" s="1">
+        <v>40052591</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>433</v>
+        <v>111</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A225" s="1">
-        <v>7093320</v>
+      <c r="A225" s="1" t="s">
+        <v>440</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>211</v>
+        <v>470</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
-        <v>40105597</v>
+        <v>41929747</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>178</v>
+        <v>471</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>461</v>
+        <v>368</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>496</v>
+        <v>112</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A229" s="1">
-        <v>20659538</v>
+      <c r="A229" s="1" t="s">
+        <v>369</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>179</v>
+        <v>113</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
-        <v>40782264</v>
+        <v>7093320</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>116</v>
+        <v>204</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A231" s="1">
-        <v>76465704</v>
+      <c r="A231" s="1" t="s">
+        <v>370</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>117</v>
+        <v>182</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A232" s="1" t="s">
-        <v>386</v>
+      <c r="A232" s="1">
+        <v>40105597</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>118</v>
+        <v>174</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
-        <v>387</v>
+        <v>441</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>119</v>
+        <v>472</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A234" s="1" t="s">
-        <v>388</v>
+      <c r="A234" s="1">
+        <v>20659538</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
-        <v>10663914</v>
+        <v>40782264</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A236" s="1" t="s">
-        <v>462</v>
+      <c r="A236" s="1">
+        <v>76465704</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>497</v>
+        <v>115</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
-        <v>463</v>
+        <v>371</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>498</v>
+        <v>116</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>187</v>
+        <v>118</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A240" s="1" t="s">
-        <v>391</v>
+      <c r="A240" s="1">
+        <v>10663914</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>434</v>
+        <v>119</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
-        <v>392</v>
+        <v>442</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>123</v>
+        <v>473</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>393</v>
+        <v>443</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>124</v>
+        <v>474</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
-        <v>464</v>
+        <v>374</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>499</v>
+        <v>120</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A244" s="1">
-        <v>42198740</v>
+      <c r="A244" s="1" t="s">
+        <v>496</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>125</v>
+        <v>517</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
-        <v>465</v>
+        <v>375</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>500</v>
+        <v>183</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>180</v>
+        <v>417</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>435</v>
+        <v>121</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
-        <v>397</v>
+        <v>444</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>188</v>
+        <v>475</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A250" s="1" t="s">
-        <v>398</v>
+      <c r="A250" s="1">
+        <v>42198740</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A251" s="1">
-        <v>71741888</v>
+      <c r="A251" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>212</v>
+        <v>476</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>436</v>
+        <v>176</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>128</v>
+        <v>418</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A254" s="1">
-        <v>44202404</v>
+      <c r="A254" s="1" t="s">
+        <v>381</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>213</v>
+        <v>124</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>437</v>
+        <v>184</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
-        <v>72637021</v>
+        <v>71741888</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>403</v>
+        <v>384</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>130</v>
+        <v>419</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
-        <v>466</v>
+        <v>385</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>501</v>
+        <v>126</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A260" s="1" t="s">
-        <v>404</v>
+      <c r="A260" s="1">
+        <v>44202404</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>131</v>
+        <v>420</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A263" s="1" t="s">
-        <v>407</v>
+      <c r="A263" s="1">
+        <v>72637021</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
-        <v>467</v>
+        <v>388</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>502</v>
+        <v>128</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>133</v>
+        <v>477</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A266" s="1">
-        <v>43928099</v>
+      <c r="A266" s="1" t="s">
+        <v>497</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>148</v>
+        <v>518</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>503</v>
+        <v>519</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>215</v>
+        <v>129</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>136</v>
+        <v>178</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A272" s="1">
-        <v>48434434</v>
+      <c r="A272" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>216</v>
+        <v>478</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A273" s="1" t="s">
-        <v>413</v>
+      <c r="A273" s="1">
+        <v>20025594</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>438</v>
+        <v>520</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
-        <v>40188806</v>
+        <v>6645374</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>504</v>
+        <v>521</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A276" s="1" t="s">
-        <v>415</v>
+      <c r="A276" s="1">
+        <v>43928099</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>439</v>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A277" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A278" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A279" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A280" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A281" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A282" s="1">
+        <v>48434434</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A283" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A284" s="1">
+        <v>40188806</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A285" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A286" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>422</v>
       </c>
     </row>
   </sheetData>
